--- a/订单信息.xlsx
+++ b/订单信息.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F201"/>
+  <dimension ref="A1:G201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,15 +434,20 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>品牌</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>商品名称</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>购买量</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>订单金额（元）</t>
         </is>
@@ -459,18 +464,25 @@
           <t>2025-09-08 10:30</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>1</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>000001</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>iPhone 15 Pro Max</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
       <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
         <v>5949.15</v>
       </c>
     </row>
@@ -485,18 +497,25 @@
           <t>2025-09-15 14:20</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>1</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>000001</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>AirPods Pro 2</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
       <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
         <v>1519.2</v>
       </c>
     </row>
@@ -511,18 +530,25 @@
           <t>2025-09-25 08:10</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>000002</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Galaxy S23 Ultra</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Galaxy S23 Ultra</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>8398.6</v>
       </c>
     </row>
@@ -537,18 +563,25 @@
           <t>2025-10-02 19:45</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>2</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>000002</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Galaxy Buds2 Pro</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
       <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
         <v>674.25</v>
       </c>
     </row>
@@ -563,18 +596,25 @@
           <t>2025-10-12 11:05</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>3</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>000003</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>MacBook Air M2</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
       <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
         <v>7599.2</v>
       </c>
     </row>
@@ -589,18 +629,25 @@
           <t>2025-10-21 16:35</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>3</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>000003</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>iPad 10</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
       <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
         <v>3059.15</v>
       </c>
     </row>
@@ -615,18 +662,25 @@
           <t>2025-11-01 09:50</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>3</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>000003</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>Sony</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>WH-1000XM5</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
       <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
         <v>2099.3</v>
       </c>
     </row>
@@ -641,18 +695,25 @@
           <t>2025-11-11 22:10</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>4</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>000004</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>13 Ultra</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
       <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
         <v>4999</v>
       </c>
     </row>
@@ -667,18 +728,25 @@
           <t>2025-11-22 13:25</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>4</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>000004</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>Pad 5</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
       <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
         <v>2999</v>
       </c>
     </row>
@@ -693,18 +761,25 @@
           <t>2025-12-02 07:40</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>4</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>000004</t>
+        </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>Watch S1</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
       <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
         <v>899.1</v>
       </c>
     </row>
@@ -719,18 +794,25 @@
           <t>2025-12-10 18:00</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>5</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>000005</t>
+        </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>Huawei</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>P60 Pro</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>2</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>7998.4</v>
       </c>
     </row>
@@ -745,18 +827,25 @@
           <t>2025-12-20 12:15</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>5</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>000005</t>
+        </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>FreeBuds Pro 3</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
       <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
         <v>909.3</v>
       </c>
     </row>
@@ -771,18 +860,25 @@
           <t>2025-12-30 20:30</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>5</v>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>000005</t>
+        </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>Huawei</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>MatePad Pro</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
       <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
         <v>3199.2</v>
       </c>
     </row>
@@ -797,18 +893,25 @@
           <t>2026-01-05 08:55</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>5</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>000005</t>
+        </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>Logitech</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>MX Keys</t>
         </is>
       </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
       <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
         <v>719.2</v>
       </c>
     </row>
@@ -823,18 +926,25 @@
           <t>2026-01-15 15:10</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>6</v>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>000006</t>
+        </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>Galaxy A54</t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
       <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
         <v>2379.15</v>
       </c>
     </row>
@@ -849,18 +959,25 @@
           <t>2026-01-25 21:45</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>6</v>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>000006</t>
+        </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>Galaxy Tab S8</t>
         </is>
       </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
       <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
         <v>4124.25</v>
       </c>
     </row>
@@ -875,18 +992,25 @@
           <t>2026-02-02 10:20</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>6</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>000006</t>
+        </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>小米</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>Buds 4 Pro</t>
         </is>
       </c>
-      <c r="E18" t="n">
-        <v>1</v>
-      </c>
       <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
         <v>599</v>
       </c>
     </row>
@@ -901,18 +1025,25 @@
           <t>2026-02-14 17:05</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>7</v>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>000007</t>
+        </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>Huawei</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>Mate 60 Pro</t>
         </is>
       </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
       <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
         <v>5999</v>
       </c>
     </row>
@@ -927,18 +1058,25 @@
           <t>2026-02-26 14:30</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>7</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>000007</t>
+        </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>Huawei</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>Watch GT4</t>
         </is>
       </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
       <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
         <v>1510.4</v>
       </c>
     </row>
@@ -953,18 +1091,25 @@
           <t>2026-03-03 09:00</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>7</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>000007</t>
+        </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E21" t="n">
-        <v>1</v>
-      </c>
       <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
         <v>2249.25</v>
       </c>
     </row>
@@ -979,18 +1124,25 @@
           <t>2026-03-13 19:15</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>7</v>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>000007</t>
+        </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>Logitech</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>G502</t>
         </is>
       </c>
-      <c r="E22" t="n">
-        <v>1</v>
-      </c>
       <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
         <v>424.15</v>
       </c>
     </row>
@@ -1005,18 +1157,25 @@
           <t>2026-03-24 12:40</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>8</v>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>000008</t>
+        </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>Pixel 7</t>
         </is>
       </c>
-      <c r="E23" t="n">
-        <v>1</v>
-      </c>
       <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
         <v>2924.25</v>
       </c>
     </row>
@@ -1031,18 +1190,25 @@
           <t>2026-04-01 16:50</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>8</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>000008</t>
+        </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>Pixel Slate</t>
         </is>
       </c>
-      <c r="E24" t="n">
-        <v>1</v>
-      </c>
       <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
         <v>2174.25</v>
       </c>
     </row>
@@ -1057,18 +1223,25 @@
           <t>2026-04-11 22:25</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>8</v>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>000008</t>
+        </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>Beats</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>Studio Buds+</t>
         </is>
       </c>
-      <c r="E25" t="n">
-        <v>1</v>
-      </c>
       <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
         <v>879.2</v>
       </c>
     </row>
@@ -1083,18 +1256,25 @@
           <t>2026-04-22 07:30</t>
         </is>
       </c>
-      <c r="C26" t="n">
-        <v>8</v>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>000008</t>
+        </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>Dell</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>UltraSharp U2723QE</t>
         </is>
       </c>
-      <c r="E26" t="n">
-        <v>1</v>
-      </c>
       <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="n">
         <v>3199.2</v>
       </c>
     </row>
@@ -1109,18 +1289,25 @@
           <t>2026-05-03 18:10</t>
         </is>
       </c>
-      <c r="C27" t="n">
-        <v>9</v>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>000009</t>
+        </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>X80</t>
         </is>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>2</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>2718.3</v>
       </c>
     </row>
@@ -1135,18 +1322,25 @@
           <t>2026-05-14 11:55</t>
         </is>
       </c>
-      <c r="C28" t="n">
-        <v>9</v>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>000009</t>
+        </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>Bose</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>QC Earbuds II</t>
         </is>
       </c>
-      <c r="E28" t="n">
-        <v>1</v>
-      </c>
       <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="n">
         <v>1444.15</v>
       </c>
     </row>
@@ -1161,18 +1355,25 @@
           <t>2026-05-25 20:35</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>9</v>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>000009</t>
+        </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>Spectre x360 14</t>
         </is>
       </c>
-      <c r="E29" t="n">
-        <v>1</v>
-      </c>
       <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
         <v>5999.25</v>
       </c>
     </row>
@@ -1187,18 +1388,25 @@
           <t>2026-06-04 13:45</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>9</v>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>000009</t>
+        </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>Charge 5</t>
         </is>
       </c>
-      <c r="E30" t="n">
-        <v>1</v>
-      </c>
       <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="n">
         <v>999</v>
       </c>
     </row>
@@ -1213,18 +1421,25 @@
           <t>2026-06-15 08:20</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>9</v>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>000009</t>
+        </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>Sony</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>SRS-XB43</t>
         </is>
       </c>
-      <c r="E31" t="n">
-        <v>1</v>
-      </c>
       <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="n">
         <v>1599.2</v>
       </c>
     </row>
@@ -1239,18 +1454,25 @@
           <t>2026-06-26 17:40</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v>10</v>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>000010</t>
+        </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>OnePlus</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>11 Pro</t>
         </is>
       </c>
-      <c r="E32" t="n">
-        <v>1</v>
-      </c>
       <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="n">
         <v>3439.2</v>
       </c>
     </row>
@@ -1265,18 +1487,25 @@
           <t>2026-07-06 10:15</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>10</v>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>000010</t>
+        </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>Envy 16</t>
         </is>
       </c>
-      <c r="E33" t="n">
-        <v>1</v>
-      </c>
       <c r="F33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" t="n">
         <v>7199.2</v>
       </c>
     </row>
@@ -1291,18 +1520,25 @@
           <t>2026-07-17 14:50</t>
         </is>
       </c>
-      <c r="C34" t="n">
-        <v>10</v>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>000010</t>
+        </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>Sony</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>WH-1000XM4</t>
         </is>
       </c>
-      <c r="E34" t="n">
+      <c r="F34" t="n">
         <v>2</v>
       </c>
-      <c r="F34" t="n">
+      <c r="G34" t="n">
         <v>3448.5</v>
       </c>
     </row>
@@ -1317,18 +1553,25 @@
           <t>2026-07-28 21:00</t>
         </is>
       </c>
-      <c r="C35" t="n">
-        <v>10</v>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>000010</t>
+        </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>Odyssey G7</t>
         </is>
       </c>
-      <c r="E35" t="n">
-        <v>1</v>
-      </c>
       <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="n">
         <v>4999</v>
       </c>
     </row>
@@ -1343,18 +1586,25 @@
           <t>2026-08-06 09:30</t>
         </is>
       </c>
-      <c r="C36" t="n">
-        <v>1</v>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>000001</t>
+        </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>Watch SE (2023)</t>
         </is>
       </c>
-      <c r="E36" t="n">
-        <v>1</v>
-      </c>
       <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" t="n">
         <v>2099.25</v>
       </c>
     </row>
@@ -1369,18 +1619,25 @@
           <t>2026-08-17 16:10</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>000002</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Live Pro 2</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
         <v>2</v>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Live Pro 2</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>2</v>
-      </c>
-      <c r="F37" t="n">
+      <c r="G37" t="n">
         <v>1358.3</v>
       </c>
     </row>
@@ -1395,18 +1652,25 @@
           <t>2026-08-28 12:05</t>
         </is>
       </c>
-      <c r="C38" t="n">
-        <v>3</v>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>000003</t>
+        </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t>Razer</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>BlackWidow V3 Pro</t>
         </is>
       </c>
-      <c r="E38" t="n">
-        <v>1</v>
-      </c>
       <c r="F38" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" t="n">
         <v>1299</v>
       </c>
     </row>
@@ -1421,18 +1685,25 @@
           <t>2026-09-02 18:30</t>
         </is>
       </c>
-      <c r="C39" t="n">
-        <v>6</v>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>000006</t>
+        </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t>Bose</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>SoundLink Revolve+</t>
         </is>
       </c>
-      <c r="E39" t="n">
-        <v>1</v>
-      </c>
       <c r="F39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" t="n">
         <v>2024.25</v>
       </c>
     </row>
@@ -1447,18 +1718,25 @@
           <t>2026-09-07 08:45</t>
         </is>
       </c>
-      <c r="C40" t="n">
-        <v>9</v>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>000009</t>
+        </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>ASUS</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>ProArt PA279CV</t>
         </is>
       </c>
-      <c r="E40" t="n">
-        <v>1</v>
-      </c>
       <c r="F40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" t="n">
         <v>2249.25</v>
       </c>
     </row>
@@ -1473,18 +1751,25 @@
           <t>2025-09-09 12:00</t>
         </is>
       </c>
-      <c r="C41" t="n">
-        <v>10</v>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>000010</t>
+        </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>iPad Pro 12.9</t>
         </is>
       </c>
-      <c r="E41" t="n">
-        <v>1</v>
-      </c>
       <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" t="n">
         <v>7439.2</v>
       </c>
     </row>
@@ -1499,18 +1784,25 @@
           <t>2025-09-10 08:30</t>
         </is>
       </c>
-      <c r="C42" t="n">
-        <v>11</v>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>000011</t>
+        </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>iPhone 14</t>
         </is>
       </c>
-      <c r="E42" t="n">
-        <v>1</v>
-      </c>
       <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" t="n">
         <v>4999</v>
       </c>
     </row>
@@ -1525,18 +1817,25 @@
           <t>2025-09-22 14:15</t>
         </is>
       </c>
-      <c r="C43" t="n">
-        <v>11</v>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>000011</t>
+        </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>Galaxy Buds2</t>
         </is>
       </c>
-      <c r="E43" t="n">
-        <v>1</v>
-      </c>
       <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" t="n">
         <v>699</v>
       </c>
     </row>
@@ -1551,18 +1850,25 @@
           <t>2025-10-01 11:20</t>
         </is>
       </c>
-      <c r="C44" t="n">
-        <v>11</v>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>000011</t>
+        </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t>Logitech</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>MX Master 3S</t>
         </is>
       </c>
-      <c r="E44" t="n">
-        <v>1</v>
-      </c>
       <c r="F44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" t="n">
         <v>524.25</v>
       </c>
     </row>
@@ -1577,18 +1883,25 @@
           <t>2025-10-15 19:45</t>
         </is>
       </c>
-      <c r="C45" t="n">
-        <v>12</v>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>000012</t>
+        </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>iPhone 15 Pro</t>
         </is>
       </c>
-      <c r="E45" t="n">
-        <v>1</v>
-      </c>
       <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="n">
         <v>7999</v>
       </c>
     </row>
@@ -1603,18 +1916,25 @@
           <t>2025-10-28 09:05</t>
         </is>
       </c>
-      <c r="C46" t="n">
-        <v>12</v>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>000012</t>
+        </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>iPad Air</t>
         </is>
       </c>
-      <c r="E46" t="n">
-        <v>1</v>
-      </c>
       <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="n">
         <v>4799</v>
       </c>
     </row>
@@ -1629,18 +1949,25 @@
           <t>2025-11-02 16:10</t>
         </is>
       </c>
-      <c r="C47" t="n">
-        <v>12</v>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>000012</t>
+        </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t>Sony</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>WH-1000XM4</t>
         </is>
       </c>
-      <c r="E47" t="n">
+      <c r="F47" t="n">
         <v>2</v>
       </c>
-      <c r="F47" t="n">
+      <c r="G47" t="n">
         <v>3448.5</v>
       </c>
     </row>
@@ -1655,18 +1982,25 @@
           <t>2025-11-18 22:30</t>
         </is>
       </c>
-      <c r="C48" t="n">
-        <v>12</v>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>000012</t>
+        </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>Watch Series 9</t>
         </is>
       </c>
-      <c r="E48" t="n">
-        <v>1</v>
-      </c>
       <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" t="n">
         <v>2559.2</v>
       </c>
     </row>
@@ -1681,18 +2015,25 @@
           <t>2025-11-25 12:00</t>
         </is>
       </c>
-      <c r="C49" t="n">
-        <v>12</v>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>000012</t>
+        </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t>Logitech</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>G502</t>
         </is>
       </c>
-      <c r="E49" t="n">
-        <v>1</v>
-      </c>
       <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="n">
         <v>424.15</v>
       </c>
     </row>
@@ -1707,18 +2048,25 @@
           <t>2025-12-05 07:50</t>
         </is>
       </c>
-      <c r="C50" t="n">
-        <v>13</v>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>000013</t>
+        </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
           <t>MacBook Pro 14 M2 Pro</t>
         </is>
       </c>
-      <c r="E50" t="n">
-        <v>1</v>
-      </c>
       <c r="F50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" t="n">
         <v>14999</v>
       </c>
     </row>
@@ -1733,18 +2081,25 @@
           <t>2025-12-12 20:25</t>
         </is>
       </c>
-      <c r="C51" t="n">
-        <v>13</v>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>000013</t>
+        </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t>Dell</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>XPS 13 Plus</t>
         </is>
       </c>
-      <c r="E51" t="n">
-        <v>1</v>
-      </c>
       <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" t="n">
         <v>7999.2</v>
       </c>
     </row>
@@ -1759,18 +2114,25 @@
           <t>2025-12-24 13:40</t>
         </is>
       </c>
-      <c r="C52" t="n">
-        <v>13</v>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>000013</t>
+        </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
           <t>UltraFine 27UP850</t>
         </is>
       </c>
-      <c r="E52" t="n">
-        <v>1</v>
-      </c>
       <c r="F52" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" t="n">
         <v>3059.15</v>
       </c>
     </row>
@@ -1785,18 +2147,25 @@
           <t>2026-01-03 18:15</t>
         </is>
       </c>
-      <c r="C53" t="n">
-        <v>13</v>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>000013</t>
+        </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>Surface Keyboard</t>
         </is>
       </c>
-      <c r="E53" t="n">
-        <v>1</v>
-      </c>
       <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" t="n">
         <v>279.2</v>
       </c>
     </row>
@@ -1811,18 +2180,25 @@
           <t>2026-01-14 10:55</t>
         </is>
       </c>
-      <c r="C54" t="n">
-        <v>14</v>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>000014</t>
+        </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>Galaxy S23</t>
         </is>
       </c>
-      <c r="E54" t="n">
-        <v>1</v>
-      </c>
       <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" t="n">
         <v>2799.2</v>
       </c>
     </row>
@@ -1837,18 +2213,25 @@
           <t>2026-01-27 15:35</t>
         </is>
       </c>
-      <c r="C55" t="n">
-        <v>14</v>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>000014</t>
+        </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>Pixel 7 Pro</t>
         </is>
       </c>
-      <c r="E55" t="n">
-        <v>1</v>
-      </c>
       <c r="F55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" t="n">
         <v>4999</v>
       </c>
     </row>
@@ -1863,18 +2246,25 @@
           <t>2026-02-06 08:10</t>
         </is>
       </c>
-      <c r="C56" t="n">
-        <v>14</v>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>000014</t>
+        </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t>Bose</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>QC Earbuds II</t>
         </is>
       </c>
-      <c r="E56" t="n">
-        <v>1</v>
-      </c>
       <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" t="n">
         <v>1444.15</v>
       </c>
     </row>
@@ -1889,18 +2279,25 @@
           <t>2026-02-17 21:00</t>
         </is>
       </c>
-      <c r="C57" t="n">
-        <v>15</v>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>000015</t>
+        </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t>Huawei</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>P60</t>
         </is>
       </c>
-      <c r="E57" t="n">
-        <v>1</v>
-      </c>
       <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="n">
         <v>3999</v>
       </c>
     </row>
@@ -1915,18 +2312,25 @@
           <t>2026-02-28 14:50</t>
         </is>
       </c>
-      <c r="C58" t="n">
-        <v>15</v>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>000015</t>
+        </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t>Huawei</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
           <t>MatePad</t>
         </is>
       </c>
-      <c r="E58" t="n">
-        <v>1</v>
-      </c>
       <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" t="n">
         <v>2124.15</v>
       </c>
     </row>
@@ -1941,18 +2345,25 @@
           <t>2026-03-07 09:40</t>
         </is>
       </c>
-      <c r="C59" t="n">
-        <v>15</v>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>000015</t>
+        </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
           <t>FreeBuds Pro 2</t>
         </is>
       </c>
-      <c r="E59" t="n">
-        <v>1</v>
-      </c>
       <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" t="n">
         <v>999</v>
       </c>
     </row>
@@ -1967,18 +2378,25 @@
           <t>2026-03-19 17:20</t>
         </is>
       </c>
-      <c r="C60" t="n">
-        <v>15</v>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>000015</t>
+        </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t>Garmin</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
           <t>Venu 2</t>
         </is>
       </c>
-      <c r="E60" t="n">
-        <v>1</v>
-      </c>
       <c r="F60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" t="n">
         <v>1499.25</v>
       </c>
     </row>
@@ -1993,18 +2411,25 @@
           <t>2026-03-30 12:45</t>
         </is>
       </c>
-      <c r="C61" t="n">
-        <v>15</v>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>000015</t>
+        </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t>Asus</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
           <t>ROG Zephyrus G14</t>
         </is>
       </c>
-      <c r="E61" t="n">
-        <v>1</v>
-      </c>
       <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" t="n">
         <v>9999</v>
       </c>
     </row>
@@ -2019,18 +2444,25 @@
           <t>2026-04-05 19:30</t>
         </is>
       </c>
-      <c r="C62" t="n">
-        <v>16</v>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>000016</t>
+        </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
           <t>12T</t>
         </is>
       </c>
-      <c r="E62" t="n">
-        <v>1</v>
-      </c>
       <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" t="n">
         <v>2124.15</v>
       </c>
     </row>
@@ -2045,18 +2477,25 @@
           <t>2026-04-18 07:25</t>
         </is>
       </c>
-      <c r="C63" t="n">
-        <v>16</v>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>000016</t>
+        </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
           <t>Galaxy Tab S8 Ultra</t>
         </is>
       </c>
-      <c r="E63" t="n">
-        <v>1</v>
-      </c>
       <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" t="n">
         <v>6999</v>
       </c>
     </row>
@@ -2071,18 +2510,25 @@
           <t>2026-04-29 16:05</t>
         </is>
       </c>
-      <c r="C64" t="n">
-        <v>16</v>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>000016</t>
+        </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
           <t>Galaxy Buds2 Pro</t>
         </is>
       </c>
-      <c r="E64" t="n">
-        <v>1</v>
-      </c>
       <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" t="n">
         <v>674.25</v>
       </c>
     </row>
@@ -2097,18 +2543,25 @@
           <t>2026-05-08 13:10</t>
         </is>
       </c>
-      <c r="C65" t="n">
-        <v>16</v>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>000016</t>
+        </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t>Huawei</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
           <t>Watch GT3</t>
         </is>
       </c>
-      <c r="E65" t="n">
-        <v>1</v>
-      </c>
       <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" t="n">
         <v>1264.8</v>
       </c>
     </row>
@@ -2123,18 +2576,25 @@
           <t>2026-05-20 22:15</t>
         </is>
       </c>
-      <c r="C66" t="n">
-        <v>17</v>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>000017</t>
+        </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
           <t>13 Pro</t>
         </is>
       </c>
-      <c r="E66" t="n">
-        <v>1</v>
-      </c>
       <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" t="n">
         <v>3199.2</v>
       </c>
     </row>
@@ -2149,18 +2609,25 @@
           <t>2026-05-30 10:30</t>
         </is>
       </c>
-      <c r="C67" t="n">
-        <v>17</v>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>000017</t>
+        </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>Surface Laptop 5</t>
         </is>
       </c>
-      <c r="E67" t="n">
-        <v>1</v>
-      </c>
       <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" t="n">
         <v>7039.2</v>
       </c>
     </row>
@@ -2175,18 +2642,25 @@
           <t>2026-06-09 15:50</t>
         </is>
       </c>
-      <c r="C68" t="n">
-        <v>17</v>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>000017</t>
+        </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t>Logitech</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
           <t>MX Keys</t>
         </is>
       </c>
-      <c r="E68" t="n">
-        <v>1</v>
-      </c>
       <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" t="n">
         <v>719.2</v>
       </c>
     </row>
@@ -2201,18 +2675,25 @@
           <t>2026-06-18 08:55</t>
         </is>
       </c>
-      <c r="C69" t="n">
-        <v>18</v>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>000018</t>
+        </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t>Oppo</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
           <t>Find X5</t>
         </is>
       </c>
-      <c r="E69" t="n">
-        <v>1</v>
-      </c>
       <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" t="n">
         <v>2159.2</v>
       </c>
     </row>
@@ -2227,18 +2708,25 @@
           <t>2026-06-28 20:40</t>
         </is>
       </c>
-      <c r="C70" t="n">
-        <v>18</v>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>000018</t>
+        </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t>Oppo</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
           <t>Reno9</t>
         </is>
       </c>
-      <c r="E70" t="n">
-        <v>1</v>
-      </c>
       <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" t="n">
         <v>2899</v>
       </c>
     </row>
@@ -2253,18 +2741,25 @@
           <t>2026-07-06 11:35</t>
         </is>
       </c>
-      <c r="C71" t="n">
-        <v>18</v>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>000018</t>
+        </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t>Lenovo</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
           <t>Tab P12</t>
         </is>
       </c>
-      <c r="E71" t="n">
-        <v>1</v>
-      </c>
       <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" t="n">
         <v>2639.2</v>
       </c>
     </row>
@@ -2279,18 +2774,25 @@
           <t>2026-07-15 18:20</t>
         </is>
       </c>
-      <c r="C72" t="n">
-        <v>18</v>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>000018</t>
+        </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t>Bose</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
           <t>SoundLink Revolve+</t>
         </is>
       </c>
-      <c r="E72" t="n">
-        <v>1</v>
-      </c>
       <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="n">
         <v>2024.25</v>
       </c>
     </row>
@@ -2305,18 +2807,25 @@
           <t>2026-07-26 14:10</t>
         </is>
       </c>
-      <c r="C73" t="n">
-        <v>18</v>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>000018</t>
+        </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
           <t>Charge 5</t>
         </is>
       </c>
-      <c r="E73" t="n">
-        <v>1</v>
-      </c>
       <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" t="n">
         <v>999</v>
       </c>
     </row>
@@ -2331,18 +2840,25 @@
           <t>2026-08-02 09:00</t>
         </is>
       </c>
-      <c r="C74" t="n">
-        <v>19</v>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>000019</t>
+        </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
           <t>Edge 40</t>
         </is>
       </c>
-      <c r="E74" t="n">
-        <v>1</v>
-      </c>
       <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" t="n">
         <v>2599</v>
       </c>
     </row>
@@ -2357,18 +2873,25 @@
           <t>2026-08-13 22:05</t>
         </is>
       </c>
-      <c r="C75" t="n">
-        <v>19</v>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>000019</t>
+        </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t>ASUS</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
           <t>ProArt PA279CV</t>
         </is>
       </c>
-      <c r="E75" t="n">
-        <v>1</v>
-      </c>
       <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="n">
         <v>2249.25</v>
       </c>
     </row>
@@ -2383,18 +2906,25 @@
           <t>2026-08-24 16:45</t>
         </is>
       </c>
-      <c r="C76" t="n">
-        <v>19</v>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>000019</t>
+        </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t>Razer</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
           <t>BlackWidow V3 Pro</t>
         </is>
       </c>
-      <c r="E76" t="n">
-        <v>1</v>
-      </c>
       <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" t="n">
         <v>1299</v>
       </c>
     </row>
@@ -2409,18 +2939,25 @@
           <t>2026-09-01 07:30</t>
         </is>
       </c>
-      <c r="C77" t="n">
-        <v>19</v>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>000019</t>
+        </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t>Sony</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
           <t>WH-1000XM5</t>
         </is>
       </c>
-      <c r="E77" t="n">
-        <v>1</v>
-      </c>
       <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" t="n">
         <v>2099.3</v>
       </c>
     </row>
@@ -2435,18 +2972,25 @@
           <t>2026-09-05 12:25</t>
         </is>
       </c>
-      <c r="C78" t="n">
-        <v>20</v>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>000020</t>
+        </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t>OnePlus</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E78" t="n">
-        <v>1</v>
-      </c>
       <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" t="n">
         <v>3299</v>
       </c>
     </row>
@@ -2461,18 +3005,25 @@
           <t>2026-09-07 19:10</t>
         </is>
       </c>
-      <c r="C79" t="n">
-        <v>20</v>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>000020</t>
+        </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
           <t>Watch Ultra 2</t>
         </is>
       </c>
-      <c r="E79" t="n">
-        <v>1</v>
-      </c>
       <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" t="n">
         <v>6299</v>
       </c>
     </row>
@@ -2487,18 +3038,25 @@
           <t>2026-09-08 10:50</t>
         </is>
       </c>
-      <c r="C80" t="n">
-        <v>20</v>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>000020</t>
+        </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>AirPods Max</t>
         </is>
       </c>
-      <c r="E80" t="n">
-        <v>1</v>
-      </c>
       <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" t="n">
         <v>4399</v>
       </c>
     </row>
@@ -2513,18 +3071,25 @@
           <t>2025-09-30 15:20</t>
         </is>
       </c>
-      <c r="C81" t="n">
-        <v>20</v>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>000020</t>
+        </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t>Sony</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>SRS-XB43</t>
         </is>
       </c>
-      <c r="E81" t="n">
-        <v>1</v>
-      </c>
       <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" t="n">
         <v>1599.2</v>
       </c>
     </row>
@@ -2539,18 +3104,25 @@
           <t>2025-09-20 08:30</t>
         </is>
       </c>
-      <c r="C82" t="n">
-        <v>21</v>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>000021</t>
+        </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
           <t>Tune 125</t>
         </is>
       </c>
-      <c r="E82" t="n">
-        <v>1</v>
-      </c>
       <c r="F82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" t="n">
         <v>399.2</v>
       </c>
     </row>
@@ -2565,18 +3137,25 @@
           <t>2025-10-10 10:00</t>
         </is>
       </c>
-      <c r="C83" t="n">
-        <v>22</v>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>000022</t>
+        </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
           <t>iPhone 14</t>
         </is>
       </c>
-      <c r="E83" t="n">
-        <v>1</v>
-      </c>
       <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" t="n">
         <v>4999</v>
       </c>
     </row>
@@ -2591,18 +3170,25 @@
           <t>2025-11-05 14:45</t>
         </is>
       </c>
-      <c r="C84" t="n">
-        <v>22</v>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>000022</t>
+        </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
           <t>iPad 10</t>
         </is>
       </c>
-      <c r="E84" t="n">
-        <v>1</v>
-      </c>
       <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" t="n">
         <v>3059.15</v>
       </c>
     </row>
@@ -2617,18 +3203,25 @@
           <t>2025-12-01 12:15</t>
         </is>
       </c>
-      <c r="C85" t="n">
-        <v>23</v>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>000023</t>
+        </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
           <t>Galaxy S23</t>
         </is>
       </c>
-      <c r="E85" t="n">
-        <v>1</v>
-      </c>
       <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" t="n">
         <v>2799.2</v>
       </c>
     </row>
@@ -2643,18 +3236,25 @@
           <t>2025-12-20 17:20</t>
         </is>
       </c>
-      <c r="C86" t="n">
-        <v>23</v>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>000023</t>
+        </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
           <t>Galaxy S23 Ultra</t>
         </is>
       </c>
-      <c r="E86" t="n">
-        <v>1</v>
-      </c>
       <c r="F86" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" t="n">
         <v>4199.3</v>
       </c>
     </row>
@@ -2669,18 +3269,25 @@
           <t>2026-01-10 19:00</t>
         </is>
       </c>
-      <c r="C87" t="n">
-        <v>23</v>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>000023</t>
+        </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
+          <t>Sony</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
           <t>WH-1000XM5</t>
         </is>
       </c>
-      <c r="E87" t="n">
-        <v>1</v>
-      </c>
       <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" t="n">
         <v>2099.3</v>
       </c>
     </row>
@@ -2695,18 +3302,25 @@
           <t>2026-02-01 21:30</t>
         </is>
       </c>
-      <c r="C88" t="n">
-        <v>23</v>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>000023</t>
+        </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
           <t>AirPods Pro 2</t>
         </is>
       </c>
-      <c r="E88" t="n">
-        <v>1</v>
-      </c>
       <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" t="n">
         <v>1519.2</v>
       </c>
     </row>
@@ -2721,18 +3335,25 @@
           <t>2026-02-14 08:30</t>
         </is>
       </c>
-      <c r="C89" t="n">
-        <v>23</v>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>000023</t>
+        </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
           <t>Watch Series 9</t>
         </is>
       </c>
-      <c r="E89" t="n">
-        <v>1</v>
-      </c>
       <c r="F89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" t="n">
         <v>2559.2</v>
       </c>
     </row>
@@ -2747,18 +3368,25 @@
           <t>2026-03-01 10:00</t>
         </is>
       </c>
-      <c r="C90" t="n">
-        <v>23</v>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>000023</t>
+        </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
           <t>Watch SE (2023)</t>
         </is>
       </c>
-      <c r="E90" t="n">
-        <v>1</v>
-      </c>
       <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" t="n">
         <v>2099.25</v>
       </c>
     </row>
@@ -2773,18 +3401,25 @@
           <t>2026-03-20 14:45</t>
         </is>
       </c>
-      <c r="C91" t="n">
-        <v>23</v>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>000023</t>
+        </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
           <t>iPad Air</t>
         </is>
       </c>
-      <c r="E91" t="n">
-        <v>1</v>
-      </c>
       <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" t="n">
         <v>4799</v>
       </c>
     </row>
@@ -2799,18 +3434,25 @@
           <t>2026-04-01 12:15</t>
         </is>
       </c>
-      <c r="C92" t="n">
-        <v>24</v>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>000024</t>
+        </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
           <t>MacBook Air M2</t>
         </is>
       </c>
-      <c r="E92" t="n">
-        <v>1</v>
-      </c>
       <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" t="n">
         <v>7599.2</v>
       </c>
     </row>
@@ -2825,18 +3467,25 @@
           <t>2026-04-15 17:20</t>
         </is>
       </c>
-      <c r="C93" t="n">
-        <v>24</v>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>000024</t>
+        </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
+          <t>Dell</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
           <t>UltraSharp U2723QE</t>
         </is>
       </c>
-      <c r="E93" t="n">
-        <v>1</v>
-      </c>
       <c r="F93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" t="n">
         <v>3199.2</v>
       </c>
     </row>
@@ -2851,18 +3500,25 @@
           <t>2026-04-30 19:00</t>
         </is>
       </c>
-      <c r="C94" t="n">
-        <v>24</v>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>000024</t>
+        </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
+          <t>Logitech</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
           <t>MX Keys</t>
         </is>
       </c>
-      <c r="E94" t="n">
-        <v>1</v>
-      </c>
       <c r="F94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" t="n">
         <v>719.2</v>
       </c>
     </row>
@@ -2877,18 +3533,25 @@
           <t>2026-05-05 21:30</t>
         </is>
       </c>
-      <c r="C95" t="n">
-        <v>25</v>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>000025</t>
+        </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
           <t>iPhone 15 Pro Max</t>
         </is>
       </c>
-      <c r="E95" t="n">
-        <v>1</v>
-      </c>
       <c r="F95" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" t="n">
         <v>5949.15</v>
       </c>
     </row>
@@ -2903,18 +3566,25 @@
           <t>2026-05-15 08:30</t>
         </is>
       </c>
-      <c r="C96" t="n">
-        <v>25</v>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>000025</t>
+        </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
           <t>iPhone 15 Pro</t>
         </is>
       </c>
-      <c r="E96" t="n">
-        <v>1</v>
-      </c>
       <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" t="n">
         <v>7999</v>
       </c>
     </row>
@@ -2929,18 +3599,25 @@
           <t>2026-05-25 10:00</t>
         </is>
       </c>
-      <c r="C97" t="n">
-        <v>25</v>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>000025</t>
+        </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
           <t>iPad Pro 12.9</t>
         </is>
       </c>
-      <c r="E97" t="n">
-        <v>1</v>
-      </c>
       <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" t="n">
         <v>7439.2</v>
       </c>
     </row>
@@ -2955,18 +3632,25 @@
           <t>2026-06-01 14:45</t>
         </is>
       </c>
-      <c r="C98" t="n">
-        <v>25</v>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>000025</t>
+        </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
           <t>Galaxy Tab S8</t>
         </is>
       </c>
-      <c r="E98" t="n">
-        <v>1</v>
-      </c>
       <c r="F98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" t="n">
         <v>4124.25</v>
       </c>
     </row>
@@ -2981,18 +3665,25 @@
           <t>2026-06-10 12:15</t>
         </is>
       </c>
-      <c r="C99" t="n">
-        <v>25</v>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>000025</t>
+        </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
+          <t>Sony</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
           <t>WF-1000XM5</t>
         </is>
       </c>
-      <c r="E99" t="n">
-        <v>1</v>
-      </c>
       <c r="F99" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" t="n">
         <v>1199.2</v>
       </c>
     </row>
@@ -3007,18 +3698,25 @@
           <t>2026-06-20 17:20</t>
         </is>
       </c>
-      <c r="C100" t="n">
-        <v>25</v>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>000025</t>
+        </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
+          <t>Bose</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
           <t>QC Earbuds II</t>
         </is>
       </c>
-      <c r="E100" t="n">
-        <v>1</v>
-      </c>
       <c r="F100" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" t="n">
         <v>1444.15</v>
       </c>
     </row>
@@ -3033,18 +3731,25 @@
           <t>2026-07-01 19:00</t>
         </is>
       </c>
-      <c r="C101" t="n">
-        <v>26</v>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>000026</t>
+        </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
           <t>Galaxy Watch6</t>
         </is>
       </c>
-      <c r="E101" t="n">
-        <v>1</v>
-      </c>
       <c r="F101" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" t="n">
         <v>2079.2</v>
       </c>
     </row>
@@ -3059,18 +3764,25 @@
           <t>2026-07-10 21:30</t>
         </is>
       </c>
-      <c r="C102" t="n">
-        <v>26</v>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>000026</t>
+        </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
+          <t>Huawei</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
           <t>Watch GT4</t>
         </is>
       </c>
-      <c r="E102" t="n">
-        <v>1</v>
-      </c>
       <c r="F102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" t="n">
         <v>1510.4</v>
       </c>
     </row>
@@ -3085,18 +3797,25 @@
           <t>2026-07-20 08:30</t>
         </is>
       </c>
-      <c r="C103" t="n">
-        <v>26</v>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>000026</t>
+        </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
+          <t>Sony</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
           <t>SRS-XB43</t>
         </is>
       </c>
-      <c r="E103" t="n">
-        <v>1</v>
-      </c>
       <c r="F103" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" t="n">
         <v>1599.2</v>
       </c>
     </row>
@@ -3111,18 +3830,25 @@
           <t>2026-07-30 10:00</t>
         </is>
       </c>
-      <c r="C104" t="n">
-        <v>26</v>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>000026</t>
+        </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
+          <t>Bose</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
           <t>SoundLink Revolve+</t>
         </is>
       </c>
-      <c r="E104" t="n">
-        <v>1</v>
-      </c>
       <c r="F104" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" t="n">
         <v>2024.25</v>
       </c>
     </row>
@@ -3137,18 +3863,25 @@
           <t>2026-08-01 14:45</t>
         </is>
       </c>
-      <c r="C105" t="n">
-        <v>27</v>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>000027</t>
+        </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
           <t>MacBook Pro 14 M2 Pro</t>
         </is>
       </c>
-      <c r="E105" t="n">
-        <v>1</v>
-      </c>
       <c r="F105" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" t="n">
         <v>14999</v>
       </c>
     </row>
@@ -3163,18 +3896,25 @@
           <t>2026-08-05 12:15</t>
         </is>
       </c>
-      <c r="C106" t="n">
-        <v>28</v>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>000028</t>
+        </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
+          <t>Huawei</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
           <t>P60</t>
         </is>
       </c>
-      <c r="E106" t="n">
-        <v>1</v>
-      </c>
       <c r="F106" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" t="n">
         <v>3999</v>
       </c>
     </row>
@@ -3189,18 +3929,25 @@
           <t>2026-08-10 17:20</t>
         </is>
       </c>
-      <c r="C107" t="n">
-        <v>28</v>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>000028</t>
+        </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
+          <t>Huawei</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
           <t>P60 Pro</t>
         </is>
       </c>
-      <c r="E107" t="n">
-        <v>1</v>
-      </c>
       <c r="F107" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" t="n">
         <v>3999.2</v>
       </c>
     </row>
@@ -3215,18 +3962,25 @@
           <t>2026-08-15 19:00</t>
         </is>
       </c>
-      <c r="C108" t="n">
-        <v>28</v>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>000028</t>
+        </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
+          <t>Huawei</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
           <t>MatePad Pro</t>
         </is>
       </c>
-      <c r="E108" t="n">
-        <v>1</v>
-      </c>
       <c r="F108" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" t="n">
         <v>3199.2</v>
       </c>
     </row>
@@ -3241,18 +3995,25 @@
           <t>2026-08-20 21:30</t>
         </is>
       </c>
-      <c r="C109" t="n">
-        <v>28</v>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>000028</t>
+        </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
+          <t>Huawei</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
           <t>MatePad</t>
         </is>
       </c>
-      <c r="E109" t="n">
-        <v>1</v>
-      </c>
       <c r="F109" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" t="n">
         <v>2124.15</v>
       </c>
     </row>
@@ -3267,18 +4028,25 @@
           <t>2026-08-25 08:30</t>
         </is>
       </c>
-      <c r="C110" t="n">
-        <v>28</v>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>000028</t>
+        </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
           <t>FreeBuds Pro 3</t>
         </is>
       </c>
-      <c r="E110" t="n">
-        <v>1</v>
-      </c>
       <c r="F110" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" t="n">
         <v>909.3</v>
       </c>
     </row>
@@ -3293,18 +4061,25 @@
           <t>2026-08-30 10:00</t>
         </is>
       </c>
-      <c r="C111" t="n">
-        <v>28</v>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>000028</t>
+        </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
+          <t>小米</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
           <t>Buds 4 Pro</t>
         </is>
       </c>
-      <c r="E111" t="n">
-        <v>1</v>
-      </c>
       <c r="F111" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" t="n">
         <v>599</v>
       </c>
     </row>
@@ -3319,18 +4094,25 @@
           <t>2026-09-01 14:45</t>
         </is>
       </c>
-      <c r="C112" t="n">
-        <v>28</v>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>000028</t>
+        </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
           <t>Watch Ultra 2</t>
         </is>
       </c>
-      <c r="E112" t="n">
-        <v>1</v>
-      </c>
       <c r="F112" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" t="n">
         <v>6299</v>
       </c>
     </row>
@@ -3345,18 +4127,25 @@
           <t>2026-09-05 12:15</t>
         </is>
       </c>
-      <c r="C113" t="n">
-        <v>28</v>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>000028</t>
+        </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
           <t>Galaxy Watch6 Classic</t>
         </is>
       </c>
-      <c r="E113" t="n">
-        <v>1</v>
-      </c>
       <c r="F113" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" t="n">
         <v>3299</v>
       </c>
     </row>
@@ -3371,18 +4160,25 @@
           <t>2025-10-20 17:20</t>
         </is>
       </c>
-      <c r="C114" t="n">
-        <v>29</v>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>000029</t>
+        </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E114" t="n">
-        <v>1</v>
-      </c>
       <c r="F114" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" t="n">
         <v>2249.25</v>
       </c>
     </row>
@@ -3397,18 +4193,25 @@
           <t>2025-11-15 19:00</t>
         </is>
       </c>
-      <c r="C115" t="n">
-        <v>29</v>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>000029</t>
+        </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
           <t>Pad 5</t>
         </is>
       </c>
-      <c r="E115" t="n">
-        <v>1</v>
-      </c>
       <c r="F115" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" t="n">
         <v>2999</v>
       </c>
     </row>
@@ -3423,18 +4226,25 @@
           <t>2026-01-05 21:30</t>
         </is>
       </c>
-      <c r="C116" t="n">
-        <v>29</v>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>000029</t>
+        </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
+          <t>Beats</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
           <t>Studio Buds+</t>
         </is>
       </c>
-      <c r="E116" t="n">
-        <v>1</v>
-      </c>
       <c r="F116" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" t="n">
         <v>879.2</v>
       </c>
     </row>
@@ -3449,18 +4259,25 @@
           <t>2026-02-10 08:30</t>
         </is>
       </c>
-      <c r="C117" t="n">
-        <v>29</v>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>000029</t>
+        </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
+          <t>Logitech</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
           <t>MX Master 3S</t>
         </is>
       </c>
-      <c r="E117" t="n">
-        <v>1</v>
-      </c>
       <c r="F117" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" t="n">
         <v>524.25</v>
       </c>
     </row>
@@ -3475,18 +4292,25 @@
           <t>2026-03-05 10:00</t>
         </is>
       </c>
-      <c r="C118" t="n">
-        <v>29</v>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>000029</t>
+        </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
+          <t>ASUS</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
           <t>ProArt PA279CV</t>
         </is>
       </c>
-      <c r="E118" t="n">
-        <v>1</v>
-      </c>
       <c r="F118" t="n">
+        <v>1</v>
+      </c>
+      <c r="G118" t="n">
         <v>2249.25</v>
       </c>
     </row>
@@ -3501,18 +4325,25 @@
           <t>2026-06-25 14:45</t>
         </is>
       </c>
-      <c r="C119" t="n">
-        <v>30</v>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>000030</t>
+        </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
           <t>Charge 5</t>
         </is>
       </c>
-      <c r="E119" t="n">
-        <v>1</v>
-      </c>
       <c r="F119" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" t="n">
         <v>999</v>
       </c>
     </row>
@@ -3527,18 +4358,25 @@
           <t>2026-07-15 12:15</t>
         </is>
       </c>
-      <c r="C120" t="n">
-        <v>30</v>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>000030</t>
+        </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
+          <t>Harman</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
           <t>Kardon Onyx Studio 7</t>
         </is>
       </c>
-      <c r="E120" t="n">
-        <v>1</v>
-      </c>
       <c r="F120" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" t="n">
         <v>1274.15</v>
       </c>
     </row>
@@ -3553,18 +4391,25 @@
           <t>2026-08-25 17:20</t>
         </is>
       </c>
-      <c r="C121" t="n">
-        <v>30</v>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>000030</t>
+        </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
           <t>Galaxy Buds2</t>
         </is>
       </c>
-      <c r="E121" t="n">
-        <v>1</v>
-      </c>
       <c r="F121" t="n">
+        <v>1</v>
+      </c>
+      <c r="G121" t="n">
         <v>699</v>
       </c>
     </row>
@@ -3579,18 +4424,25 @@
           <t>2025-09-25 09:10</t>
         </is>
       </c>
-      <c r="C122" t="n">
-        <v>31</v>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>000031</t>
+        </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
           <t>Galaxy A54</t>
         </is>
       </c>
-      <c r="E122" t="n">
-        <v>1</v>
-      </c>
       <c r="F122" t="n">
+        <v>1</v>
+      </c>
+      <c r="G122" t="n">
         <v>2379.15</v>
       </c>
     </row>
@@ -3605,18 +4457,25 @@
           <t>2025-10-15 16:30</t>
         </is>
       </c>
-      <c r="C123" t="n">
-        <v>32</v>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>000032</t>
+        </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
           <t>iPhone 14 Pro</t>
         </is>
       </c>
-      <c r="E123" t="n">
-        <v>1</v>
-      </c>
       <c r="F123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G123" t="n">
         <v>4799.2</v>
       </c>
     </row>
@@ -3631,18 +4490,25 @@
           <t>2025-11-02 11:20</t>
         </is>
       </c>
-      <c r="C124" t="n">
-        <v>32</v>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>000032</t>
+        </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
           <t>AirPods Max</t>
         </is>
       </c>
-      <c r="E124" t="n">
-        <v>1</v>
-      </c>
       <c r="F124" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" t="n">
         <v>4399</v>
       </c>
     </row>
@@ -3657,18 +4523,25 @@
           <t>2025-12-10 20:40</t>
         </is>
       </c>
-      <c r="C125" t="n">
-        <v>33</v>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>000033</t>
+        </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
           <t>Galaxy Tab S8 Ultra</t>
         </is>
       </c>
-      <c r="E125" t="n">
-        <v>1</v>
-      </c>
       <c r="F125" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" t="n">
         <v>6999</v>
       </c>
     </row>
@@ -3683,18 +4556,25 @@
           <t>2026-01-05 14:15</t>
         </is>
       </c>
-      <c r="C126" t="n">
-        <v>33</v>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>000033</t>
+        </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
+          <t>Sony</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
           <t>WH-1000XM4</t>
         </is>
       </c>
-      <c r="E126" t="n">
+      <c r="F126" t="n">
         <v>2</v>
       </c>
-      <c r="F126" t="n">
+      <c r="G126" t="n">
         <v>3448.5</v>
       </c>
     </row>
@@ -3709,18 +4589,25 @@
           <t>2026-02-01 08:50</t>
         </is>
       </c>
-      <c r="C127" t="n">
-        <v>34</v>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>000034</t>
+        </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
+          <t>Dell</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
           <t>XPS 15</t>
         </is>
       </c>
-      <c r="E127" t="n">
-        <v>1</v>
-      </c>
       <c r="F127" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" t="n">
         <v>11999</v>
       </c>
     </row>
@@ -3735,18 +4622,25 @@
           <t>2026-02-14 19:25</t>
         </is>
       </c>
-      <c r="C128" t="n">
-        <v>34</v>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>000034</t>
+        </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
           <t>UltraFine 27UP850</t>
         </is>
       </c>
-      <c r="E128" t="n">
-        <v>1</v>
-      </c>
       <c r="F128" t="n">
+        <v>1</v>
+      </c>
+      <c r="G128" t="n">
         <v>3059.15</v>
       </c>
     </row>
@@ -3761,18 +4655,25 @@
           <t>2026-03-01 12:00</t>
         </is>
       </c>
-      <c r="C129" t="n">
-        <v>34</v>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>000034</t>
+        </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
+          <t>Logitech</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
           <t>MX Master 3S</t>
         </is>
       </c>
-      <c r="E129" t="n">
-        <v>1</v>
-      </c>
       <c r="F129" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" t="n">
         <v>524.25</v>
       </c>
     </row>
@@ -3787,18 +4688,25 @@
           <t>2026-03-20 18:10</t>
         </is>
       </c>
-      <c r="C130" t="n">
-        <v>35</v>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>000035</t>
+        </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
+          <t>Huawei</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
           <t>Mate 60 Pro</t>
         </is>
       </c>
-      <c r="E130" t="n">
-        <v>1</v>
-      </c>
       <c r="F130" t="n">
+        <v>1</v>
+      </c>
+      <c r="G130" t="n">
         <v>5999</v>
       </c>
     </row>
@@ -3813,18 +4721,25 @@
           <t>2026-04-05 10:45</t>
         </is>
       </c>
-      <c r="C131" t="n">
-        <v>35</v>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>000035</t>
+        </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
+          <t>Huawei</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
           <t>MatePad Pro</t>
         </is>
       </c>
-      <c r="E131" t="n">
-        <v>1</v>
-      </c>
       <c r="F131" t="n">
+        <v>1</v>
+      </c>
+      <c r="G131" t="n">
         <v>3199.2</v>
       </c>
     </row>
@@ -3839,18 +4754,25 @@
           <t>2026-04-18 21:30</t>
         </is>
       </c>
-      <c r="C132" t="n">
-        <v>35</v>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>000035</t>
+        </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
           <t>FreeBuds Pro 2</t>
         </is>
       </c>
-      <c r="E132" t="n">
-        <v>1</v>
-      </c>
       <c r="F132" t="n">
+        <v>1</v>
+      </c>
+      <c r="G132" t="n">
         <v>999</v>
       </c>
     </row>
@@ -3865,18 +4787,25 @@
           <t>2026-05-02 07:15</t>
         </is>
       </c>
-      <c r="C133" t="n">
-        <v>36</v>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>000036</t>
+        </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
           <t>12T</t>
         </is>
       </c>
-      <c r="E133" t="n">
-        <v>1</v>
-      </c>
       <c r="F133" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" t="n">
         <v>2124.15</v>
       </c>
     </row>
@@ -3891,18 +4820,25 @@
           <t>2026-05-12 13:50</t>
         </is>
       </c>
-      <c r="C134" t="n">
-        <v>36</v>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>000036</t>
+        </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
+          <t>Realme</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
           <t>GT2 Pro</t>
         </is>
       </c>
-      <c r="E134" t="n">
-        <v>1</v>
-      </c>
       <c r="F134" t="n">
+        <v>1</v>
+      </c>
+      <c r="G134" t="n">
         <v>2599</v>
       </c>
     </row>
@@ -3917,18 +4853,25 @@
           <t>2026-05-22 22:05</t>
         </is>
       </c>
-      <c r="C135" t="n">
-        <v>36</v>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>000036</t>
+        </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
+          <t>小米</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
           <t>Buds 3</t>
         </is>
       </c>
-      <c r="E135" t="n">
-        <v>1</v>
-      </c>
       <c r="F135" t="n">
+        <v>1</v>
+      </c>
+      <c r="G135" t="n">
         <v>319.2</v>
       </c>
     </row>
@@ -3943,18 +4886,25 @@
           <t>2026-06-01 09:40</t>
         </is>
       </c>
-      <c r="C136" t="n">
-        <v>36</v>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>000036</t>
+        </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
           <t>Watch S2</t>
         </is>
       </c>
-      <c r="E136" t="n">
-        <v>1</v>
-      </c>
       <c r="F136" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" t="n">
         <v>1299</v>
       </c>
     </row>
@@ -3969,18 +4919,25 @@
           <t>2026-06-10 16:25</t>
         </is>
       </c>
-      <c r="C137" t="n">
-        <v>37</v>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>000037</t>
+        </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
           <t>Edge 30</t>
         </is>
       </c>
-      <c r="E137" t="n">
-        <v>1</v>
-      </c>
       <c r="F137" t="n">
+        <v>1</v>
+      </c>
+      <c r="G137" t="n">
         <v>1599.2</v>
       </c>
     </row>
@@ -3995,18 +4952,25 @@
           <t>2026-06-20 11:55</t>
         </is>
       </c>
-      <c r="C138" t="n">
-        <v>37</v>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>000037</t>
+        </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
+          <t>Lenovo</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
           <t>Tab M10</t>
         </is>
       </c>
-      <c r="E138" t="n">
-        <v>1</v>
-      </c>
       <c r="F138" t="n">
+        <v>1</v>
+      </c>
+      <c r="G138" t="n">
         <v>1999</v>
       </c>
     </row>
@@ -4021,18 +4985,25 @@
           <t>2026-07-01 20:10</t>
         </is>
       </c>
-      <c r="C139" t="n">
-        <v>37</v>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>000037</t>
+        </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
           <t>Live Pro 2</t>
         </is>
       </c>
-      <c r="E139" t="n">
-        <v>1</v>
-      </c>
       <c r="F139" t="n">
+        <v>1</v>
+      </c>
+      <c r="G139" t="n">
         <v>679.15</v>
       </c>
     </row>
@@ -4047,18 +5018,25 @@
           <t>2026-07-10 08:30</t>
         </is>
       </c>
-      <c r="C140" t="n">
-        <v>38</v>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>000038</t>
+        </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
           <t>iPhone 15 Ultra</t>
         </is>
       </c>
-      <c r="E140" t="n">
-        <v>1</v>
-      </c>
       <c r="F140" t="n">
+        <v>1</v>
+      </c>
+      <c r="G140" t="n">
         <v>6749.25</v>
       </c>
     </row>
@@ -4073,18 +5051,25 @@
           <t>2026-07-18 14:20</t>
         </is>
       </c>
-      <c r="C141" t="n">
-        <v>38</v>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>000038</t>
+        </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
           <t>iPhone 14</t>
         </is>
       </c>
-      <c r="E141" t="n">
-        <v>1</v>
-      </c>
       <c r="F141" t="n">
+        <v>1</v>
+      </c>
+      <c r="G141" t="n">
         <v>4999</v>
       </c>
     </row>
@@ -4099,18 +5084,25 @@
           <t>2026-07-26 18:45</t>
         </is>
       </c>
-      <c r="C142" t="n">
-        <v>38</v>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>000038</t>
+        </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
           <t>iPad Pro 12.9</t>
         </is>
       </c>
-      <c r="E142" t="n">
-        <v>1</v>
-      </c>
       <c r="F142" t="n">
+        <v>1</v>
+      </c>
+      <c r="G142" t="n">
         <v>7439.2</v>
       </c>
     </row>
@@ -4125,18 +5117,25 @@
           <t>2026-08-02 09:00</t>
         </is>
       </c>
-      <c r="C143" t="n">
-        <v>38</v>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>000038</t>
+        </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
           <t>iPad 10</t>
         </is>
       </c>
-      <c r="E143" t="n">
-        <v>1</v>
-      </c>
       <c r="F143" t="n">
+        <v>1</v>
+      </c>
+      <c r="G143" t="n">
         <v>3059.15</v>
       </c>
     </row>
@@ -4151,18 +5150,25 @@
           <t>2026-08-08 12:35</t>
         </is>
       </c>
-      <c r="C144" t="n">
-        <v>38</v>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>000038</t>
+        </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
           <t>AirPods Pro 2</t>
         </is>
       </c>
-      <c r="E144" t="n">
-        <v>1</v>
-      </c>
       <c r="F144" t="n">
+        <v>1</v>
+      </c>
+      <c r="G144" t="n">
         <v>1519.2</v>
       </c>
     </row>
@@ -4177,18 +5183,25 @@
           <t>2026-08-14 17:10</t>
         </is>
       </c>
-      <c r="C145" t="n">
-        <v>38</v>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>000038</t>
+        </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
+          <t>Sony</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
           <t>WH-1000XM5</t>
         </is>
       </c>
-      <c r="E145" t="n">
-        <v>1</v>
-      </c>
       <c r="F145" t="n">
+        <v>1</v>
+      </c>
+      <c r="G145" t="n">
         <v>2099.3</v>
       </c>
     </row>
@@ -4203,18 +5216,25 @@
           <t>2026-08-20 21:55</t>
         </is>
       </c>
-      <c r="C146" t="n">
-        <v>38</v>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>000038</t>
+        </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
           <t>Watch Ultra 2</t>
         </is>
       </c>
-      <c r="E146" t="n">
-        <v>1</v>
-      </c>
       <c r="F146" t="n">
+        <v>1</v>
+      </c>
+      <c r="G146" t="n">
         <v>6299</v>
       </c>
     </row>
@@ -4229,18 +5249,25 @@
           <t>2026-08-26 07:40</t>
         </is>
       </c>
-      <c r="C147" t="n">
-        <v>38</v>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>000038</t>
+        </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
           <t>Galaxy Watch6 Classic</t>
         </is>
       </c>
-      <c r="E147" t="n">
-        <v>1</v>
-      </c>
       <c r="F147" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" t="n">
         <v>3299</v>
       </c>
     </row>
@@ -4255,18 +5282,25 @@
           <t>2026-09-01 13:15</t>
         </is>
       </c>
-      <c r="C148" t="n">
-        <v>39</v>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>000039</t>
+        </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
           <t>Pixel 6a</t>
         </is>
       </c>
-      <c r="E148" t="n">
-        <v>1</v>
-      </c>
       <c r="F148" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" t="n">
         <v>1359.2</v>
       </c>
     </row>
@@ -4281,18 +5315,25 @@
           <t>2026-09-03 19:30</t>
         </is>
       </c>
-      <c r="C149" t="n">
-        <v>39</v>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>000039</t>
+        </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
           <t>Pixel Slate</t>
         </is>
       </c>
-      <c r="E149" t="n">
-        <v>1</v>
-      </c>
       <c r="F149" t="n">
+        <v>1</v>
+      </c>
+      <c r="G149" t="n">
         <v>2174.25</v>
       </c>
     </row>
@@ -4307,18 +5348,25 @@
           <t>2026-09-05 10:50</t>
         </is>
       </c>
-      <c r="C150" t="n">
-        <v>39</v>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>000039</t>
+        </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
+          <t>Beats</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
           <t>Studio Buds+</t>
         </is>
       </c>
-      <c r="E150" t="n">
-        <v>1</v>
-      </c>
       <c r="F150" t="n">
+        <v>1</v>
+      </c>
+      <c r="G150" t="n">
         <v>879.2</v>
       </c>
     </row>
@@ -4333,18 +5381,25 @@
           <t>2026-09-07 16:05</t>
         </is>
       </c>
-      <c r="C151" t="n">
-        <v>39</v>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>000039</t>
+        </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
           <t>Surface Keyboard</t>
         </is>
       </c>
-      <c r="E151" t="n">
-        <v>1</v>
-      </c>
       <c r="F151" t="n">
+        <v>1</v>
+      </c>
+      <c r="G151" t="n">
         <v>279.2</v>
       </c>
     </row>
@@ -4359,18 +5414,25 @@
           <t>2026-09-08 08:25</t>
         </is>
       </c>
-      <c r="C152" t="n">
-        <v>39</v>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>000039</t>
+        </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
+          <t>ASUS</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
           <t>ProArt PA279CV</t>
         </is>
       </c>
-      <c r="E152" t="n">
-        <v>1</v>
-      </c>
       <c r="F152" t="n">
+        <v>1</v>
+      </c>
+      <c r="G152" t="n">
         <v>2249.25</v>
       </c>
     </row>
@@ -4385,18 +5447,25 @@
           <t>2025-10-25 14:50</t>
         </is>
       </c>
-      <c r="C153" t="n">
-        <v>40</v>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>000040</t>
+        </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
           <t>13 Pro</t>
         </is>
       </c>
-      <c r="E153" t="n">
-        <v>1</v>
-      </c>
       <c r="F153" t="n">
+        <v>1</v>
+      </c>
+      <c r="G153" t="n">
         <v>3199.2</v>
       </c>
     </row>
@@ -4411,18 +5480,25 @@
           <t>2025-11-20 09:30</t>
         </is>
       </c>
-      <c r="C154" t="n">
-        <v>40</v>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>000040</t>
+        </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
+          <t>Sony</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
           <t>SRS-XB43</t>
         </is>
       </c>
-      <c r="E154" t="n">
-        <v>1</v>
-      </c>
       <c r="F154" t="n">
+        <v>1</v>
+      </c>
+      <c r="G154" t="n">
         <v>1599.2</v>
       </c>
     </row>
@@ -4437,18 +5513,25 @@
           <t>2025-12-25 18:15</t>
         </is>
       </c>
-      <c r="C155" t="n">
-        <v>40</v>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>000040</t>
+        </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
           <t>Pad 6 Pro</t>
         </is>
       </c>
-      <c r="E155" t="n">
-        <v>1</v>
-      </c>
       <c r="F155" t="n">
+        <v>1</v>
+      </c>
+      <c r="G155" t="n">
         <v>2799.3</v>
       </c>
     </row>
@@ -4463,18 +5546,25 @@
           <t>2026-01-30 11:40</t>
         </is>
       </c>
-      <c r="C156" t="n">
-        <v>40</v>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>000040</t>
+        </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
           <t>V27</t>
         </is>
       </c>
-      <c r="E156" t="n">
-        <v>1</v>
-      </c>
       <c r="F156" t="n">
+        <v>1</v>
+      </c>
+      <c r="G156" t="n">
         <v>1759.2</v>
       </c>
     </row>
@@ -4489,18 +5579,25 @@
           <t>2026-02-28 22:20</t>
         </is>
       </c>
-      <c r="C157" t="n">
-        <v>40</v>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>000040</t>
+        </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
           <t>Galaxy Buds2 Pro</t>
         </is>
       </c>
-      <c r="E157" t="n">
-        <v>1</v>
-      </c>
       <c r="F157" t="n">
+        <v>1</v>
+      </c>
+      <c r="G157" t="n">
         <v>674.25</v>
       </c>
     </row>
@@ -4515,18 +5612,25 @@
           <t>2026-03-25 08:10</t>
         </is>
       </c>
-      <c r="C158" t="n">
-        <v>40</v>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>000040</t>
+        </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
+          <t>Bose</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
           <t>QC Earbuds II</t>
         </is>
       </c>
-      <c r="E158" t="n">
-        <v>1</v>
-      </c>
       <c r="F158" t="n">
+        <v>1</v>
+      </c>
+      <c r="G158" t="n">
         <v>1444.15</v>
       </c>
     </row>
@@ -4541,18 +5645,25 @@
           <t>2026-04-20 13:55</t>
         </is>
       </c>
-      <c r="C159" t="n">
-        <v>40</v>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>000040</t>
+        </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
+          <t>Huawei</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
           <t>Watch GT3</t>
         </is>
       </c>
-      <c r="E159" t="n">
-        <v>1</v>
-      </c>
       <c r="F159" t="n">
+        <v>1</v>
+      </c>
+      <c r="G159" t="n">
         <v>1264.8</v>
       </c>
     </row>
@@ -4567,18 +5678,25 @@
           <t>2026-05-18 17:40</t>
         </is>
       </c>
-      <c r="C160" t="n">
-        <v>40</v>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>000040</t>
+        </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
+          <t>Asus</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
           <t>ROG Zephyrus G14</t>
         </is>
       </c>
-      <c r="E160" t="n">
-        <v>1</v>
-      </c>
       <c r="F160" t="n">
+        <v>1</v>
+      </c>
+      <c r="G160" t="n">
         <v>9999</v>
       </c>
     </row>
@@ -4593,18 +5711,25 @@
           <t>2026-06-15 09:20</t>
         </is>
       </c>
-      <c r="C161" t="n">
-        <v>40</v>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>000040</t>
+        </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
           <t>Odyssey G7</t>
         </is>
       </c>
-      <c r="E161" t="n">
-        <v>1</v>
-      </c>
       <c r="F161" t="n">
+        <v>1</v>
+      </c>
+      <c r="G161" t="n">
         <v>4999</v>
       </c>
     </row>
@@ -4619,18 +5744,25 @@
           <t>2025-09-25 09:10</t>
         </is>
       </c>
-      <c r="C162" t="n">
-        <v>41</v>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>000041</t>
+        </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
           <t>iPhone 14</t>
         </is>
       </c>
-      <c r="E162" t="n">
-        <v>1</v>
-      </c>
       <c r="F162" t="n">
+        <v>1</v>
+      </c>
+      <c r="G162" t="n">
         <v>4999</v>
       </c>
     </row>
@@ -4645,18 +5777,25 @@
           <t>2025-10-04 14:25</t>
         </is>
       </c>
-      <c r="C163" t="n">
-        <v>42</v>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>000042</t>
+        </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
           <t>Galaxy S23</t>
         </is>
       </c>
-      <c r="E163" t="n">
-        <v>1</v>
-      </c>
       <c r="F163" t="n">
+        <v>1</v>
+      </c>
+      <c r="G163" t="n">
         <v>2799.2</v>
       </c>
     </row>
@@ -4671,18 +5810,25 @@
           <t>2025-10-13 11:35</t>
         </is>
       </c>
-      <c r="C164" t="n">
-        <v>42</v>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>000042</t>
+        </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
           <t>Galaxy Buds2</t>
         </is>
       </c>
-      <c r="E164" t="n">
-        <v>1</v>
-      </c>
       <c r="F164" t="n">
+        <v>1</v>
+      </c>
+      <c r="G164" t="n">
         <v>699</v>
       </c>
     </row>
@@ -4697,18 +5843,25 @@
           <t>2025-10-22 16:50</t>
         </is>
       </c>
-      <c r="C165" t="n">
-        <v>43</v>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>000043</t>
+        </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
+          <t>Huawei</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
           <t>P60</t>
         </is>
       </c>
-      <c r="E165" t="n">
-        <v>1</v>
-      </c>
       <c r="F165" t="n">
+        <v>1</v>
+      </c>
+      <c r="G165" t="n">
         <v>3999</v>
       </c>
     </row>
@@ -4723,18 +5876,25 @@
           <t>2025-10-31 08:05</t>
         </is>
       </c>
-      <c r="C166" t="n">
-        <v>43</v>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>000043</t>
+        </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
+          <t>Huawei</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
           <t>MatePad</t>
         </is>
       </c>
-      <c r="E166" t="n">
-        <v>1</v>
-      </c>
       <c r="F166" t="n">
+        <v>1</v>
+      </c>
+      <c r="G166" t="n">
         <v>2124.15</v>
       </c>
     </row>
@@ -4749,18 +5909,25 @@
           <t>2025-11-09 12:40</t>
         </is>
       </c>
-      <c r="C167" t="n">
-        <v>43</v>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>000043</t>
+        </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
           <t>FreeBuds Pro 2</t>
         </is>
       </c>
-      <c r="E167" t="n">
-        <v>1</v>
-      </c>
       <c r="F167" t="n">
+        <v>1</v>
+      </c>
+      <c r="G167" t="n">
         <v>999</v>
       </c>
     </row>
@@ -4775,18 +5942,25 @@
           <t>2025-11-18 17:55</t>
         </is>
       </c>
-      <c r="C168" t="n">
-        <v>44</v>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>000044</t>
+        </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E168" t="n">
-        <v>1</v>
-      </c>
       <c r="F168" t="n">
+        <v>1</v>
+      </c>
+      <c r="G168" t="n">
         <v>2249.25</v>
       </c>
     </row>
@@ -4801,18 +5975,25 @@
           <t>2025-11-27 10:15</t>
         </is>
       </c>
-      <c r="C169" t="n">
-        <v>44</v>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>000044</t>
+        </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
           <t>Pad 5</t>
         </is>
       </c>
-      <c r="E169" t="n">
-        <v>1</v>
-      </c>
       <c r="F169" t="n">
+        <v>1</v>
+      </c>
+      <c r="G169" t="n">
         <v>2999</v>
       </c>
     </row>
@@ -4827,18 +6008,25 @@
           <t>2025-12-06 19:30</t>
         </is>
       </c>
-      <c r="C170" t="n">
-        <v>44</v>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>000044</t>
+        </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
+          <t>Sony</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
           <t>WF-1000XM5</t>
         </is>
       </c>
-      <c r="E170" t="n">
-        <v>1</v>
-      </c>
       <c r="F170" t="n">
+        <v>1</v>
+      </c>
+      <c r="G170" t="n">
         <v>1199.2</v>
       </c>
     </row>
@@ -4853,18 +6041,25 @@
           <t>2025-12-15 13:45</t>
         </is>
       </c>
-      <c r="C171" t="n">
-        <v>44</v>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>000044</t>
+        </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
           <t>Watch SE (2023)</t>
         </is>
       </c>
-      <c r="E171" t="n">
-        <v>1</v>
-      </c>
       <c r="F171" t="n">
+        <v>1</v>
+      </c>
+      <c r="G171" t="n">
         <v>2099.25</v>
       </c>
     </row>
@@ -4879,18 +6074,25 @@
           <t>2025-12-24 21:00</t>
         </is>
       </c>
-      <c r="C172" t="n">
-        <v>45</v>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>000045</t>
+        </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
+          <t>OnePlus</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E172" t="n">
-        <v>1</v>
-      </c>
       <c r="F172" t="n">
+        <v>1</v>
+      </c>
+      <c r="G172" t="n">
         <v>3299</v>
       </c>
     </row>
@@ -4905,18 +6107,25 @@
           <t>2026-01-02 08:30</t>
         </is>
       </c>
-      <c r="C173" t="n">
-        <v>45</v>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>000045</t>
+        </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
+          <t>Lenovo</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
           <t>Tab P12</t>
         </is>
       </c>
-      <c r="E173" t="n">
-        <v>1</v>
-      </c>
       <c r="F173" t="n">
+        <v>1</v>
+      </c>
+      <c r="G173" t="n">
         <v>2639.2</v>
       </c>
     </row>
@@ -4931,18 +6140,25 @@
           <t>2026-01-11 15:10</t>
         </is>
       </c>
-      <c r="C174" t="n">
-        <v>45</v>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>000045</t>
+        </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
+          <t>Bose</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
           <t>QuietComfort 45</t>
         </is>
       </c>
-      <c r="E174" t="n">
-        <v>1</v>
-      </c>
       <c r="F174" t="n">
+        <v>1</v>
+      </c>
+      <c r="G174" t="n">
         <v>1299</v>
       </c>
     </row>
@@ -4957,18 +6173,25 @@
           <t>2026-01-20 11:55</t>
         </is>
       </c>
-      <c r="C175" t="n">
-        <v>45</v>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>000045</t>
+        </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
           <t>Galaxy Watch6</t>
         </is>
       </c>
-      <c r="E175" t="n">
-        <v>1</v>
-      </c>
       <c r="F175" t="n">
+        <v>1</v>
+      </c>
+      <c r="G175" t="n">
         <v>2079.2</v>
       </c>
     </row>
@@ -4983,18 +6206,25 @@
           <t>2026-01-29 18:20</t>
         </is>
       </c>
-      <c r="C176" t="n">
-        <v>45</v>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>000045</t>
+        </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
+          <t>Acer</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
           <t>Swift 3</t>
         </is>
       </c>
-      <c r="E176" t="n">
-        <v>1</v>
-      </c>
       <c r="F176" t="n">
+        <v>1</v>
+      </c>
+      <c r="G176" t="n">
         <v>4799.2</v>
       </c>
     </row>
@@ -5009,18 +6239,25 @@
           <t>2026-02-07 09:45</t>
         </is>
       </c>
-      <c r="C177" t="n">
-        <v>46</v>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>000046</t>
+        </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
           <t>Edge 40</t>
         </is>
       </c>
-      <c r="E177" t="n">
-        <v>1</v>
-      </c>
       <c r="F177" t="n">
+        <v>1</v>
+      </c>
+      <c r="G177" t="n">
         <v>2599</v>
       </c>
     </row>
@@ -5035,18 +6272,25 @@
           <t>2026-02-16 14:05</t>
         </is>
       </c>
-      <c r="C178" t="n">
-        <v>46</v>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>000046</t>
+        </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
+          <t>Lenovo</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
           <t>Tab M10</t>
         </is>
       </c>
-      <c r="E178" t="n">
-        <v>1</v>
-      </c>
       <c r="F178" t="n">
+        <v>1</v>
+      </c>
+      <c r="G178" t="n">
         <v>1999</v>
       </c>
     </row>
@@ -5061,18 +6305,25 @@
           <t>2026-02-25 16:35</t>
         </is>
       </c>
-      <c r="C179" t="n">
-        <v>46</v>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>000046</t>
+        </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
+          <t>Beats</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
           <t>Studio Buds+</t>
         </is>
       </c>
-      <c r="E179" t="n">
-        <v>1</v>
-      </c>
       <c r="F179" t="n">
+        <v>1</v>
+      </c>
+      <c r="G179" t="n">
         <v>879.2</v>
       </c>
     </row>
@@ -5087,18 +6338,25 @@
           <t>2026-03-06 12:25</t>
         </is>
       </c>
-      <c r="C180" t="n">
-        <v>46</v>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>000046</t>
+        </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
+          <t>Huawei</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
           <t>Watch GT3</t>
         </is>
       </c>
-      <c r="E180" t="n">
-        <v>1</v>
-      </c>
       <c r="F180" t="n">
+        <v>1</v>
+      </c>
+      <c r="G180" t="n">
         <v>1264.8</v>
       </c>
     </row>
@@ -5113,18 +6371,25 @@
           <t>2026-03-15 20:15</t>
         </is>
       </c>
-      <c r="C181" t="n">
-        <v>46</v>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>000046</t>
+        </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
+          <t>Acer</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
           <t>Aspire 5</t>
         </is>
       </c>
-      <c r="E181" t="n">
-        <v>1</v>
-      </c>
       <c r="F181" t="n">
+        <v>1</v>
+      </c>
+      <c r="G181" t="n">
         <v>7499</v>
       </c>
     </row>
@@ -5139,18 +6404,25 @@
           <t>2026-03-24 07:50</t>
         </is>
       </c>
-      <c r="C182" t="n">
-        <v>46</v>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>000046</t>
+        </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
+          <t>AOC</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
           <t>U27U2D</t>
         </is>
       </c>
-      <c r="E182" t="n">
-        <v>1</v>
-      </c>
       <c r="F182" t="n">
+        <v>1</v>
+      </c>
+      <c r="G182" t="n">
         <v>1799.1</v>
       </c>
     </row>
@@ -5165,18 +6437,25 @@
           <t>2026-04-02 13:10</t>
         </is>
       </c>
-      <c r="C183" t="n">
-        <v>47</v>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>000047</t>
+        </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
           <t>X80</t>
         </is>
       </c>
-      <c r="E183" t="n">
-        <v>1</v>
-      </c>
       <c r="F183" t="n">
+        <v>1</v>
+      </c>
+      <c r="G183" t="n">
         <v>1359.15</v>
       </c>
     </row>
@@ -5191,18 +6470,25 @@
           <t>2026-04-11 17:00</t>
         </is>
       </c>
-      <c r="C184" t="n">
-        <v>47</v>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>000047</t>
+        </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
           <t>Pixel Slate</t>
         </is>
       </c>
-      <c r="E184" t="n">
-        <v>1</v>
-      </c>
       <c r="F184" t="n">
+        <v>1</v>
+      </c>
+      <c r="G184" t="n">
         <v>2174.25</v>
       </c>
     </row>
@@ -5217,18 +6503,25 @@
           <t>2026-04-20 10:50</t>
         </is>
       </c>
-      <c r="C185" t="n">
-        <v>47</v>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>000047</t>
+        </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
           <t>Tune 125</t>
         </is>
       </c>
-      <c r="E185" t="n">
-        <v>1</v>
-      </c>
       <c r="F185" t="n">
+        <v>1</v>
+      </c>
+      <c r="G185" t="n">
         <v>399.2</v>
       </c>
     </row>
@@ -5243,18 +6536,25 @@
           <t>2026-04-29 19:05</t>
         </is>
       </c>
-      <c r="C186" t="n">
-        <v>47</v>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>000047</t>
+        </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
           <t>Watch S1</t>
         </is>
       </c>
-      <c r="E186" t="n">
-        <v>1</v>
-      </c>
       <c r="F186" t="n">
+        <v>1</v>
+      </c>
+      <c r="G186" t="n">
         <v>899.1</v>
       </c>
     </row>
@@ -5269,18 +6569,25 @@
           <t>2026-05-08 08:40</t>
         </is>
       </c>
-      <c r="C187" t="n">
-        <v>47</v>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>000047</t>
+        </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
+          <t>Lenovo</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
           <t>IdeaPad 5 Pro</t>
         </is>
       </c>
-      <c r="E187" t="n">
-        <v>1</v>
-      </c>
       <c r="F187" t="n">
+        <v>1</v>
+      </c>
+      <c r="G187" t="n">
         <v>5949.15</v>
       </c>
     </row>
@@ -5295,18 +6602,25 @@
           <t>2026-05-17 15:35</t>
         </is>
       </c>
-      <c r="C188" t="n">
-        <v>47</v>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>000047</t>
+        </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
           <t>UltraFine 27UP850</t>
         </is>
       </c>
-      <c r="E188" t="n">
-        <v>1</v>
-      </c>
       <c r="F188" t="n">
+        <v>1</v>
+      </c>
+      <c r="G188" t="n">
         <v>3059.15</v>
       </c>
     </row>
@@ -5321,18 +6635,25 @@
           <t>2026-05-26 11:10</t>
         </is>
       </c>
-      <c r="C189" t="n">
-        <v>47</v>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>000047</t>
+        </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
+          <t>Logitech</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
           <t>MX Keys</t>
         </is>
       </c>
-      <c r="E189" t="n">
-        <v>1</v>
-      </c>
       <c r="F189" t="n">
+        <v>1</v>
+      </c>
+      <c r="G189" t="n">
         <v>719.2</v>
       </c>
     </row>
@@ -5347,18 +6668,25 @@
           <t>2026-06-04 18:50</t>
         </is>
       </c>
-      <c r="C190" t="n">
-        <v>48</v>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>000048</t>
+        </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
+          <t>Oppo</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
           <t>Find X5</t>
         </is>
       </c>
-      <c r="E190" t="n">
-        <v>1</v>
-      </c>
       <c r="F190" t="n">
+        <v>1</v>
+      </c>
+      <c r="G190" t="n">
         <v>2159.2</v>
       </c>
     </row>
@@ -5373,18 +6701,25 @@
           <t>2026-06-13 09:55</t>
         </is>
       </c>
-      <c r="C191" t="n">
-        <v>48</v>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>000048</t>
+        </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
+          <t>Oppo</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
           <t>Reno9</t>
         </is>
       </c>
-      <c r="E191" t="n">
-        <v>1</v>
-      </c>
       <c r="F191" t="n">
+        <v>1</v>
+      </c>
+      <c r="G191" t="n">
         <v>2899</v>
       </c>
     </row>
@@ -5399,18 +6734,25 @@
           <t>2026-06-22 14:40</t>
         </is>
       </c>
-      <c r="C192" t="n">
-        <v>48</v>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>000048</t>
+        </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
           <t>Pad 6 Pro</t>
         </is>
       </c>
-      <c r="E192" t="n">
-        <v>1</v>
-      </c>
       <c r="F192" t="n">
+        <v>1</v>
+      </c>
+      <c r="G192" t="n">
         <v>2799.3</v>
       </c>
     </row>
@@ -5425,18 +6767,25 @@
           <t>2026-07-01 16:15</t>
         </is>
       </c>
-      <c r="C193" t="n">
-        <v>48</v>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>000048</t>
+        </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
           <t>Live Pro 2</t>
         </is>
       </c>
-      <c r="E193" t="n">
-        <v>1</v>
-      </c>
       <c r="F193" t="n">
+        <v>1</v>
+      </c>
+      <c r="G193" t="n">
         <v>679.15</v>
       </c>
     </row>
@@ -5451,18 +6800,25 @@
           <t>2026-07-10 12:55</t>
         </is>
       </c>
-      <c r="C194" t="n">
-        <v>48</v>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>000048</t>
+        </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
+          <t>小米</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
           <t>Buds 3</t>
         </is>
       </c>
-      <c r="E194" t="n">
-        <v>1</v>
-      </c>
       <c r="F194" t="n">
+        <v>1</v>
+      </c>
+      <c r="G194" t="n">
         <v>319.2</v>
       </c>
     </row>
@@ -5477,18 +6833,25 @@
           <t>2026-07-19 20:45</t>
         </is>
       </c>
-      <c r="C195" t="n">
-        <v>48</v>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>000048</t>
+        </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
           <t>Watch S2</t>
         </is>
       </c>
-      <c r="E195" t="n">
-        <v>1</v>
-      </c>
       <c r="F195" t="n">
+        <v>1</v>
+      </c>
+      <c r="G195" t="n">
         <v>1299</v>
       </c>
     </row>
@@ -5503,18 +6866,25 @@
           <t>2026-07-28 08:00</t>
         </is>
       </c>
-      <c r="C196" t="n">
-        <v>48</v>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>000048</t>
+        </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
+          <t>Asus</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
           <t>ZenBook 14 OLED</t>
         </is>
       </c>
-      <c r="E196" t="n">
-        <v>1</v>
-      </c>
       <c r="F196" t="n">
+        <v>1</v>
+      </c>
+      <c r="G196" t="n">
         <v>6449.25</v>
       </c>
     </row>
@@ -5529,18 +6899,25 @@
           <t>2026-08-06 13:35</t>
         </is>
       </c>
-      <c r="C197" t="n">
-        <v>48</v>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>000048</t>
+        </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
           <t>Charge 5</t>
         </is>
       </c>
-      <c r="E197" t="n">
-        <v>1</v>
-      </c>
       <c r="F197" t="n">
+        <v>1</v>
+      </c>
+      <c r="G197" t="n">
         <v>999</v>
       </c>
     </row>
@@ -5555,18 +6932,25 @@
           <t>2026-08-15 17:45</t>
         </is>
       </c>
-      <c r="C198" t="n">
-        <v>49</v>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>000049</t>
+        </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
+          <t>Realme</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
           <t>GT Neo3</t>
         </is>
       </c>
-      <c r="E198" t="n">
-        <v>1</v>
-      </c>
       <c r="F198" t="n">
+        <v>1</v>
+      </c>
+      <c r="G198" t="n">
         <v>1599.2</v>
       </c>
     </row>
@@ -5581,18 +6965,25 @@
           <t>2026-08-24 10:30</t>
         </is>
       </c>
-      <c r="C199" t="n">
-        <v>49</v>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>000049</t>
+        </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
+          <t>Huawei</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
           <t>MatePad Pro</t>
         </is>
       </c>
-      <c r="E199" t="n">
-        <v>1</v>
-      </c>
       <c r="F199" t="n">
+        <v>1</v>
+      </c>
+      <c r="G199" t="n">
         <v>3199.2</v>
       </c>
     </row>
@@ -5607,18 +6998,25 @@
           <t>2026-09-02 19:20</t>
         </is>
       </c>
-      <c r="C200" t="n">
-        <v>49</v>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>000049</t>
+        </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
+          <t>Sony</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
           <t>WH-1000XM5</t>
         </is>
       </c>
-      <c r="E200" t="n">
-        <v>1</v>
-      </c>
       <c r="F200" t="n">
+        <v>1</v>
+      </c>
+      <c r="G200" t="n">
         <v>2099.3</v>
       </c>
     </row>
@@ -5633,18 +7031,25 @@
           <t>2026-09-08 21:30</t>
         </is>
       </c>
-      <c r="C201" t="n">
-        <v>50</v>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>000050</t>
+        </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
           <t>iPhone 14 Pro</t>
         </is>
       </c>
-      <c r="E201" t="n">
-        <v>1</v>
-      </c>
       <c r="F201" t="n">
+        <v>1</v>
+      </c>
+      <c r="G201" t="n">
         <v>4799.2</v>
       </c>
     </row>

--- a/订单信息.xlsx
+++ b/订单信息.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G201"/>
+  <dimension ref="A1:I201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,16 @@
           <t>订单金额（元）</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>电话</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>地址</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -485,6 +495,14 @@
       <c r="G2" t="n">
         <v>5949.15</v>
       </c>
+      <c r="H2" t="n">
+        <v>13910234567</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>北京市朝阳区建国路88号SOHO现代城A座1203室</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -518,6 +536,14 @@
       <c r="G3" t="n">
         <v>1519.2</v>
       </c>
+      <c r="H3" t="n">
+        <v>13910234567</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>北京市朝阳区建国路88号SOHO现代城A座1203室</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,6 +577,14 @@
       <c r="G4" t="n">
         <v>8398.6</v>
       </c>
+      <c r="H4" t="n">
+        <v>13820345678</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>北京市海淀区中关村大街22号中科大厦B座1206室</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -584,6 +618,14 @@
       <c r="G5" t="n">
         <v>674.25</v>
       </c>
+      <c r="H5" t="n">
+        <v>13820345678</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>北京市海淀区中关村大街22号中科大厦B座1206室</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -617,6 +659,14 @@
       <c r="G6" t="n">
         <v>7599.2</v>
       </c>
+      <c r="H6" t="n">
+        <v>13730456789</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>北京市东城区东长安街1号东方广场东一办公楼801室</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -650,6 +700,14 @@
       <c r="G7" t="n">
         <v>3059.15</v>
       </c>
+      <c r="H7" t="n">
+        <v>13730456789</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>北京市东城区东长安街1号东方广场东一办公楼801室</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -683,6 +741,14 @@
       <c r="G8" t="n">
         <v>2099.3</v>
       </c>
+      <c r="H8" t="n">
+        <v>13730456789</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>北京市东城区东长安街1号东方广场东一办公楼801室</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -716,6 +782,14 @@
       <c r="G9" t="n">
         <v>4999</v>
       </c>
+      <c r="H9" t="n">
+        <v>13640567890</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>北京市西城区金融大街35号国际企业大厦B座1102室</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -749,6 +823,14 @@
       <c r="G10" t="n">
         <v>2999</v>
       </c>
+      <c r="H10" t="n">
+        <v>13640567890</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>北京市西城区金融大街35号国际企业大厦B座1102室</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -782,6 +864,14 @@
       <c r="G11" t="n">
         <v>899.1</v>
       </c>
+      <c r="H11" t="n">
+        <v>13640567890</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>北京市西城区金融大街35号国际企业大厦B座1102室</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -815,6 +905,14 @@
       <c r="G12" t="n">
         <v>7998.4</v>
       </c>
+      <c r="H12" t="n">
+        <v>13550678901</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>北京市丰台区南三环西路16号搜宝商务中心3号楼2206室</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -848,6 +946,14 @@
       <c r="G13" t="n">
         <v>909.3</v>
       </c>
+      <c r="H13" t="n">
+        <v>13550678901</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>北京市丰台区南三环西路16号搜宝商务中心3号楼2206室</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -881,6 +987,14 @@
       <c r="G14" t="n">
         <v>3199.2</v>
       </c>
+      <c r="H14" t="n">
+        <v>13550678901</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>北京市丰台区南三环西路16号搜宝商务中心3号楼2206室</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -914,6 +1028,14 @@
       <c r="G15" t="n">
         <v>719.2</v>
       </c>
+      <c r="H15" t="n">
+        <v>13550678901</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>北京市丰台区南三环西路16号搜宝商务中心3号楼2206室</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -947,6 +1069,14 @@
       <c r="G16" t="n">
         <v>2379.15</v>
       </c>
+      <c r="H16" t="n">
+        <v>15060789012</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>上海市浦东新区陆家嘴环路1000号恒生银行大厦18F</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -980,6 +1110,14 @@
       <c r="G17" t="n">
         <v>4124.25</v>
       </c>
+      <c r="H17" t="n">
+        <v>15060789012</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>上海市浦东新区陆家嘴环路1000号恒生银行大厦18F</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1013,6 +1151,14 @@
       <c r="G18" t="n">
         <v>599</v>
       </c>
+      <c r="H18" t="n">
+        <v>15060789012</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>上海市浦东新区陆家嘴环路1000号恒生银行大厦18F</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1046,6 +1192,14 @@
       <c r="G19" t="n">
         <v>5999</v>
       </c>
+      <c r="H19" t="n">
+        <v>15170890123</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>上海市静安区南京西路1717号会德丰国际广场12B</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1079,6 +1233,14 @@
       <c r="G20" t="n">
         <v>1510.4</v>
       </c>
+      <c r="H20" t="n">
+        <v>15170890123</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>上海市静安区南京西路1717号会德丰国际广场12B</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1112,6 +1274,14 @@
       <c r="G21" t="n">
         <v>2249.25</v>
       </c>
+      <c r="H21" t="n">
+        <v>15170890123</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>上海市静安区南京西路1717号会德丰国际广场12B</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1145,6 +1315,14 @@
       <c r="G22" t="n">
         <v>424.15</v>
       </c>
+      <c r="H22" t="n">
+        <v>15170890123</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>上海市静安区南京西路1717号会德丰国际广场12B</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1178,6 +1356,14 @@
       <c r="G23" t="n">
         <v>2924.25</v>
       </c>
+      <c r="H23" t="n">
+        <v>15280901234</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>上海市徐汇区虹桥路3号港汇恒隆广场二座3602</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1211,6 +1397,14 @@
       <c r="G24" t="n">
         <v>2174.25</v>
       </c>
+      <c r="H24" t="n">
+        <v>15280901234</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>上海市徐汇区虹桥路3号港汇恒隆广场二座3602</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1244,6 +1438,14 @@
       <c r="G25" t="n">
         <v>879.2</v>
       </c>
+      <c r="H25" t="n">
+        <v>15280901234</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>上海市徐汇区虹桥路3号港汇恒隆广场二座3602</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1277,6 +1479,14 @@
       <c r="G26" t="n">
         <v>3199.2</v>
       </c>
+      <c r="H26" t="n">
+        <v>15280901234</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>上海市徐汇区虹桥路3号港汇恒隆广场二座3602</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1310,6 +1520,14 @@
       <c r="G27" t="n">
         <v>2718.3</v>
       </c>
+      <c r="H27" t="n">
+        <v>15790912345</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>上海市黄浦区中山东二路600号外滩金融中心S1栋2904</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1343,6 +1561,14 @@
       <c r="G28" t="n">
         <v>1444.15</v>
       </c>
+      <c r="H28" t="n">
+        <v>15790912345</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>上海市黄浦区中山东二路600号外滩金融中心S1栋2904</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1376,6 +1602,14 @@
       <c r="G29" t="n">
         <v>5999.25</v>
       </c>
+      <c r="H29" t="n">
+        <v>15790912345</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>上海市黄浦区中山东二路600号外滩金融中心S1栋2904</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1409,6 +1643,14 @@
       <c r="G30" t="n">
         <v>999</v>
       </c>
+      <c r="H30" t="n">
+        <v>15790912345</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>上海市黄浦区中山东二路600号外滩金融中心S1栋2904</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1442,6 +1684,14 @@
       <c r="G31" t="n">
         <v>1599.2</v>
       </c>
+      <c r="H31" t="n">
+        <v>15790912345</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>上海市黄浦区中山东二路600号外滩金融中心S1栋2904</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1475,6 +1725,14 @@
       <c r="G32" t="n">
         <v>3439.2</v>
       </c>
+      <c r="H32" t="n">
+        <v>15801023456</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>上海市长宁区延安西路728号华敏翰尊国际大厦20D</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1508,6 +1766,14 @@
       <c r="G33" t="n">
         <v>7199.2</v>
       </c>
+      <c r="H33" t="n">
+        <v>15801023456</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>上海市长宁区延安西路728号华敏翰尊国际大厦20D</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1541,6 +1807,14 @@
       <c r="G34" t="n">
         <v>3448.5</v>
       </c>
+      <c r="H34" t="n">
+        <v>15801023456</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>上海市长宁区延安西路728号华敏翰尊国际大厦20D</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1574,6 +1848,14 @@
       <c r="G35" t="n">
         <v>4999</v>
       </c>
+      <c r="H35" t="n">
+        <v>15801023456</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>上海市长宁区延安西路728号华敏翰尊国际大厦20D</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1607,6 +1889,14 @@
       <c r="G36" t="n">
         <v>2099.25</v>
       </c>
+      <c r="H36" t="n">
+        <v>13910234567</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>北京市朝阳区建国路88号SOHO现代城A座1203室</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1640,6 +1930,14 @@
       <c r="G37" t="n">
         <v>1358.3</v>
       </c>
+      <c r="H37" t="n">
+        <v>13820345678</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>北京市海淀区中关村大街22号中科大厦B座1206室</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1673,6 +1971,14 @@
       <c r="G38" t="n">
         <v>1299</v>
       </c>
+      <c r="H38" t="n">
+        <v>13730456789</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>北京市东城区东长安街1号东方广场东一办公楼801室</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1706,6 +2012,14 @@
       <c r="G39" t="n">
         <v>2024.25</v>
       </c>
+      <c r="H39" t="n">
+        <v>15060789012</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>上海市浦东新区陆家嘴环路1000号恒生银行大厦18F</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1739,6 +2053,14 @@
       <c r="G40" t="n">
         <v>2249.25</v>
       </c>
+      <c r="H40" t="n">
+        <v>15790912345</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>上海市黄浦区中山东二路600号外滩金融中心S1栋2904</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1772,6 +2094,14 @@
       <c r="G41" t="n">
         <v>7439.2</v>
       </c>
+      <c r="H41" t="n">
+        <v>15801023456</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>上海市长宁区延安西路728号华敏翰尊国际大厦20D</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1805,6 +2135,14 @@
       <c r="G42" t="n">
         <v>4999</v>
       </c>
+      <c r="H42" t="n">
+        <v>15911123457</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>广州市天河区天河路385号太古汇办公楼一座2504</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1838,6 +2176,14 @@
       <c r="G43" t="n">
         <v>699</v>
       </c>
+      <c r="H43" t="n">
+        <v>15911123457</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>广州市天河区天河路385号太古汇办公楼一座2504</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1871,6 +2217,14 @@
       <c r="G44" t="n">
         <v>524.25</v>
       </c>
+      <c r="H44" t="n">
+        <v>15911123457</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>广州市天河区天河路385号太古汇办公楼一座2504</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1904,6 +2258,14 @@
       <c r="G45" t="n">
         <v>7999</v>
       </c>
+      <c r="H45" t="n">
+        <v>18021234568</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>广州市海珠区阅江中路382号保利国际广场南塔1902</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1937,6 +2299,14 @@
       <c r="G46" t="n">
         <v>4799</v>
       </c>
+      <c r="H46" t="n">
+        <v>18021234568</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>广州市海珠区阅江中路382号保利国际广场南塔1902</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1970,6 +2340,14 @@
       <c r="G47" t="n">
         <v>3448.5</v>
       </c>
+      <c r="H47" t="n">
+        <v>18021234568</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>广州市海珠区阅江中路382号保利国际广场南塔1902</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2003,6 +2381,14 @@
       <c r="G48" t="n">
         <v>2559.2</v>
       </c>
+      <c r="H48" t="n">
+        <v>18021234568</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>广州市海珠区阅江中路382号保利国际广场南塔1902</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2036,6 +2422,14 @@
       <c r="G49" t="n">
         <v>424.15</v>
       </c>
+      <c r="H49" t="n">
+        <v>18021234568</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>广州市海珠区阅江中路382号保利国际广场南塔1902</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2069,6 +2463,14 @@
       <c r="G50" t="n">
         <v>14999</v>
       </c>
+      <c r="H50" t="n">
+        <v>18131345679</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>广州市番禺区万博商务区汉溪大道东390号四海城商业广场2栋1501</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2102,6 +2504,14 @@
       <c r="G51" t="n">
         <v>7999.2</v>
       </c>
+      <c r="H51" t="n">
+        <v>18131345679</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>广州市番禺区万博商务区汉溪大道东390号四海城商业广场2栋1501</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2135,6 +2545,14 @@
       <c r="G52" t="n">
         <v>3059.15</v>
       </c>
+      <c r="H52" t="n">
+        <v>18131345679</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>广州市番禺区万博商务区汉溪大道东390号四海城商业广场2栋1501</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2168,6 +2586,14 @@
       <c r="G53" t="n">
         <v>279.2</v>
       </c>
+      <c r="H53" t="n">
+        <v>18131345679</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>广州市番禺区万博商务区汉溪大道东390号四海城商业广场2栋1501</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2201,6 +2627,14 @@
       <c r="G54" t="n">
         <v>2799.2</v>
       </c>
+      <c r="H54" t="n">
+        <v>18241456780</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>广州市荔湾区中山七路50号西门口广场写字楼A座903</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2234,6 +2668,14 @@
       <c r="G55" t="n">
         <v>4999</v>
       </c>
+      <c r="H55" t="n">
+        <v>18241456780</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>广州市荔湾区中山七路50号西门口广场写字楼A座903</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2267,6 +2709,14 @@
       <c r="G56" t="n">
         <v>1444.15</v>
       </c>
+      <c r="H56" t="n">
+        <v>18241456780</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>广州市荔湾区中山七路50号西门口广场写字楼A座903</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2300,6 +2750,14 @@
       <c r="G57" t="n">
         <v>3999</v>
       </c>
+      <c r="H57" t="n">
+        <v>18351567891</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>广州市越秀区环市东路339号广东国际大厦主楼1405</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2333,6 +2791,14 @@
       <c r="G58" t="n">
         <v>2124.15</v>
       </c>
+      <c r="H58" t="n">
+        <v>18351567891</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>广州市越秀区环市东路339号广东国际大厦主楼1405</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2366,6 +2832,14 @@
       <c r="G59" t="n">
         <v>999</v>
       </c>
+      <c r="H59" t="n">
+        <v>18351567891</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>广州市越秀区环市东路339号广东国际大厦主楼1405</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2399,6 +2873,14 @@
       <c r="G60" t="n">
         <v>1499.25</v>
       </c>
+      <c r="H60" t="n">
+        <v>18351567891</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>广州市越秀区环市东路339号广东国际大厦主楼1405</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2432,6 +2914,14 @@
       <c r="G61" t="n">
         <v>9999</v>
       </c>
+      <c r="H61" t="n">
+        <v>18351567891</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>广州市越秀区环市东路339号广东国际大厦主楼1405</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2465,6 +2955,14 @@
       <c r="G62" t="n">
         <v>2124.15</v>
       </c>
+      <c r="H62" t="n">
+        <v>18461678902</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>深圳市南山区粤海街道海天二路19号深圳湾创业投资大厦3201</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2498,6 +2996,14 @@
       <c r="G63" t="n">
         <v>6999</v>
       </c>
+      <c r="H63" t="n">
+        <v>18461678902</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>深圳市南山区粤海街道海天二路19号深圳湾创业投资大厦3201</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2531,6 +3037,14 @@
       <c r="G64" t="n">
         <v>674.25</v>
       </c>
+      <c r="H64" t="n">
+        <v>18461678902</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>深圳市南山区粤海街道海天二路19号深圳湾创业投资大厦3201</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2564,6 +3078,14 @@
       <c r="G65" t="n">
         <v>1264.8</v>
       </c>
+      <c r="H65" t="n">
+        <v>18461678902</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>深圳市南山区粤海街道海天二路19号深圳湾创业投资大厦3201</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2597,6 +3119,14 @@
       <c r="G66" t="n">
         <v>3199.2</v>
       </c>
+      <c r="H66" t="n">
+        <v>18571789013</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>深圳市福田区益田路6003号荣超商务中心B座2805</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2630,6 +3160,14 @@
       <c r="G67" t="n">
         <v>7039.2</v>
       </c>
+      <c r="H67" t="n">
+        <v>18571789013</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>深圳市福田区益田路6003号荣超商务中心B座2805</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2663,6 +3201,14 @@
       <c r="G68" t="n">
         <v>719.2</v>
       </c>
+      <c r="H68" t="n">
+        <v>18571789013</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>深圳市福田区益田路6003号荣超商务中心B座2805</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2696,6 +3242,14 @@
       <c r="G69" t="n">
         <v>2159.2</v>
       </c>
+      <c r="H69" t="n">
+        <v>18681890124</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>深圳市龙岗区坂田街道五和大道南4012号天安云谷一期3栋C座1706</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2729,6 +3283,14 @@
       <c r="G70" t="n">
         <v>2899</v>
       </c>
+      <c r="H70" t="n">
+        <v>18681890124</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>深圳市龙岗区坂田街道五和大道南4012号天安云谷一期3栋C座1706</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2762,6 +3324,14 @@
       <c r="G71" t="n">
         <v>2639.2</v>
       </c>
+      <c r="H71" t="n">
+        <v>18681890124</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>深圳市龙岗区坂田街道五和大道南4012号天安云谷一期3栋C座1706</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2795,6 +3365,14 @@
       <c r="G72" t="n">
         <v>2024.25</v>
       </c>
+      <c r="H72" t="n">
+        <v>18681890124</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>深圳市龙岗区坂田街道五和大道南4012号天安云谷一期3栋C座1706</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2828,6 +3406,14 @@
       <c r="G73" t="n">
         <v>999</v>
       </c>
+      <c r="H73" t="n">
+        <v>18681890124</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>深圳市龙岗区坂田街道五和大道南4012号天安云谷一期3栋C座1706</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2861,6 +3447,14 @@
       <c r="G74" t="n">
         <v>2599</v>
       </c>
+      <c r="H74" t="n">
+        <v>18791901235</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>深圳市宝安区新安街道创业二路99号勤诚达大厦2102</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2894,6 +3488,14 @@
       <c r="G75" t="n">
         <v>2249.25</v>
       </c>
+      <c r="H75" t="n">
+        <v>18791901235</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>深圳市宝安区新安街道创业二路99号勤诚达大厦2102</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2927,6 +3529,14 @@
       <c r="G76" t="n">
         <v>1299</v>
       </c>
+      <c r="H76" t="n">
+        <v>18791901235</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>深圳市宝安区新安街道创业二路99号勤诚达大厦2102</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2960,6 +3570,14 @@
       <c r="G77" t="n">
         <v>2099.3</v>
       </c>
+      <c r="H77" t="n">
+        <v>18791901235</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>深圳市宝安区新安街道创业二路99号勤诚达大厦2102</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2993,6 +3611,14 @@
       <c r="G78" t="n">
         <v>3299</v>
       </c>
+      <c r="H78" t="n">
+        <v>18802012346</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>深圳市龙华区观澜街道观澜大道152号观澜商务中心301</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3026,6 +3652,14 @@
       <c r="G79" t="n">
         <v>6299</v>
       </c>
+      <c r="H79" t="n">
+        <v>18802012346</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>深圳市龙华区观澜街道观澜大道152号观澜商务中心301</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3059,6 +3693,14 @@
       <c r="G80" t="n">
         <v>4399</v>
       </c>
+      <c r="H80" t="n">
+        <v>18802012346</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>深圳市龙华区观澜街道观澜大道152号观澜商务中心301</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3092,6 +3734,14 @@
       <c r="G81" t="n">
         <v>1599.2</v>
       </c>
+      <c r="H81" t="n">
+        <v>18802012346</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>深圳市龙华区观澜街道观澜大道152号观澜商务中心301</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3125,6 +3775,14 @@
       <c r="G82" t="n">
         <v>399.2</v>
       </c>
+      <c r="H82" t="n">
+        <v>18912123457</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>成都市武侯区人民南路四段27号商鼎国际大厦1号楼1506</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3158,6 +3816,14 @@
       <c r="G83" t="n">
         <v>4999</v>
       </c>
+      <c r="H83" t="n">
+        <v>13022234568</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>成都市青羊区提督街1号雄飞中心2203</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3191,6 +3857,14 @@
       <c r="G84" t="n">
         <v>3059.15</v>
       </c>
+      <c r="H84" t="n">
+        <v>13022234568</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>成都市青羊区提督街1号雄飞中心2203</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3224,6 +3898,14 @@
       <c r="G85" t="n">
         <v>2799.2</v>
       </c>
+      <c r="H85" t="n">
+        <v>13132345679</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>成都市锦江区东大街芷泉段68号时代8号写字楼1201</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3257,6 +3939,14 @@
       <c r="G86" t="n">
         <v>4199.3</v>
       </c>
+      <c r="H86" t="n">
+        <v>13132345679</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>成都市锦江区东大街芷泉段68号时代8号写字楼1201</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3290,6 +3980,14 @@
       <c r="G87" t="n">
         <v>2099.3</v>
       </c>
+      <c r="H87" t="n">
+        <v>13132345679</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>成都市锦江区东大街芷泉段68号时代8号写字楼1201</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3323,6 +4021,14 @@
       <c r="G88" t="n">
         <v>1519.2</v>
       </c>
+      <c r="H88" t="n">
+        <v>13132345679</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>成都市锦江区东大街芷泉段68号时代8号写字楼1201</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3356,6 +4062,14 @@
       <c r="G89" t="n">
         <v>2559.2</v>
       </c>
+      <c r="H89" t="n">
+        <v>13132345679</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>成都市锦江区东大街芷泉段68号时代8号写字楼1201</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3389,6 +4103,14 @@
       <c r="G90" t="n">
         <v>2099.25</v>
       </c>
+      <c r="H90" t="n">
+        <v>13132345679</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>成都市锦江区东大街芷泉段68号时代8号写字楼1201</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3422,6 +4144,14 @@
       <c r="G91" t="n">
         <v>4799</v>
       </c>
+      <c r="H91" t="n">
+        <v>13132345679</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>成都市锦江区东大街芷泉段68号时代8号写字楼1201</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3455,6 +4185,14 @@
       <c r="G92" t="n">
         <v>7599.2</v>
       </c>
+      <c r="H92" t="n">
+        <v>13242456780</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>杭州市西湖区文三路90号东部软件园创新大厦A座801</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3488,6 +4226,14 @@
       <c r="G93" t="n">
         <v>3199.2</v>
       </c>
+      <c r="H93" t="n">
+        <v>13242456780</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>杭州市西湖区文三路90号东部软件园创新大厦A座801</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3521,6 +4267,14 @@
       <c r="G94" t="n">
         <v>719.2</v>
       </c>
+      <c r="H94" t="n">
+        <v>13242456780</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>杭州市西湖区文三路90号东部软件园创新大厦A座801</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3554,6 +4308,14 @@
       <c r="G95" t="n">
         <v>5949.15</v>
       </c>
+      <c r="H95" t="n">
+        <v>13352567891</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>杭州市滨江区江南大道3588号恒生大厦B座1702</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3587,6 +4349,14 @@
       <c r="G96" t="n">
         <v>7999</v>
       </c>
+      <c r="H96" t="n">
+        <v>13352567891</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>杭州市滨江区江南大道3588号恒生大厦B座1702</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3620,6 +4390,14 @@
       <c r="G97" t="n">
         <v>7439.2</v>
       </c>
+      <c r="H97" t="n">
+        <v>13352567891</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>杭州市滨江区江南大道3588号恒生大厦B座1702</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3653,6 +4431,14 @@
       <c r="G98" t="n">
         <v>4124.25</v>
       </c>
+      <c r="H98" t="n">
+        <v>13352567891</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>杭州市滨江区江南大道3588号恒生大厦B座1702</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3686,6 +4472,14 @@
       <c r="G99" t="n">
         <v>1199.2</v>
       </c>
+      <c r="H99" t="n">
+        <v>13352567891</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>杭州市滨江区江南大道3588号恒生大厦B座1702</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3719,6 +4513,14 @@
       <c r="G100" t="n">
         <v>1444.15</v>
       </c>
+      <c r="H100" t="n">
+        <v>13352567891</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>杭州市滨江区江南大道3588号恒生大厦B座1702</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3752,6 +4554,14 @@
       <c r="G101" t="n">
         <v>2079.2</v>
       </c>
+      <c r="H101" t="n">
+        <v>13462678902</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>杭州市拱墅区湖墅南路186号美达丽阳国际商务中心905</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3785,6 +4595,14 @@
       <c r="G102" t="n">
         <v>1510.4</v>
       </c>
+      <c r="H102" t="n">
+        <v>13462678902</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>杭州市拱墅区湖墅南路186号美达丽阳国际商务中心905</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3818,6 +4636,14 @@
       <c r="G103" t="n">
         <v>1599.2</v>
       </c>
+      <c r="H103" t="n">
+        <v>13462678902</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>杭州市拱墅区湖墅南路186号美达丽阳国际商务中心905</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3851,6 +4677,14 @@
       <c r="G104" t="n">
         <v>2024.25</v>
       </c>
+      <c r="H104" t="n">
+        <v>13462678902</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>杭州市拱墅区湖墅南路186号美达丽阳国际商务中心905</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3884,6 +4718,14 @@
       <c r="G105" t="n">
         <v>14999</v>
       </c>
+      <c r="H105" t="n">
+        <v>13572789013</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>武汉市洪山区珞瑜路726号华乐商务中心1805</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3917,6 +4759,14 @@
       <c r="G106" t="n">
         <v>3999</v>
       </c>
+      <c r="H106" t="n">
+        <v>13682890124</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>武汉市江汉区解放大道686号世贸大厦写字楼2501</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3950,6 +4800,14 @@
       <c r="G107" t="n">
         <v>3999.2</v>
       </c>
+      <c r="H107" t="n">
+        <v>13682890124</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>武汉市江汉区解放大道686号世贸大厦写字楼2501</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3983,6 +4841,14 @@
       <c r="G108" t="n">
         <v>3199.2</v>
       </c>
+      <c r="H108" t="n">
+        <v>13682890124</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>武汉市江汉区解放大道686号世贸大厦写字楼2501</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4016,6 +4882,14 @@
       <c r="G109" t="n">
         <v>2124.15</v>
       </c>
+      <c r="H109" t="n">
+        <v>13682890124</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>武汉市江汉区解放大道686号世贸大厦写字楼2501</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4049,6 +4923,14 @@
       <c r="G110" t="n">
         <v>909.3</v>
       </c>
+      <c r="H110" t="n">
+        <v>13682890124</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>武汉市江汉区解放大道686号世贸大厦写字楼2501</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4082,6 +4964,14 @@
       <c r="G111" t="n">
         <v>599</v>
       </c>
+      <c r="H111" t="n">
+        <v>13682890124</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>武汉市江汉区解放大道686号世贸大厦写字楼2501</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4115,6 +5005,14 @@
       <c r="G112" t="n">
         <v>6299</v>
       </c>
+      <c r="H112" t="n">
+        <v>13682890124</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>武汉市江汉区解放大道686号世贸大厦写字楼2501</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4148,6 +5046,14 @@
       <c r="G113" t="n">
         <v>3299</v>
       </c>
+      <c r="H113" t="n">
+        <v>13682890124</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>武汉市江汉区解放大道686号世贸大厦写字楼2501</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4181,6 +5087,14 @@
       <c r="G114" t="n">
         <v>2249.25</v>
       </c>
+      <c r="H114" t="n">
+        <v>13792901235</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>南京市建邺区河西新城江东中路229号新地中心二期12A</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4214,6 +5128,14 @@
       <c r="G115" t="n">
         <v>2999</v>
       </c>
+      <c r="H115" t="n">
+        <v>13792901235</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>南京市建邺区河西新城江东中路229号新地中心二期12A</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4247,6 +5169,14 @@
       <c r="G116" t="n">
         <v>879.2</v>
       </c>
+      <c r="H116" t="n">
+        <v>13792901235</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>南京市建邺区河西新城江东中路229号新地中心二期12A</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4280,6 +5210,14 @@
       <c r="G117" t="n">
         <v>524.25</v>
       </c>
+      <c r="H117" t="n">
+        <v>13792901235</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>南京市建邺区河西新城江东中路229号新地中心二期12A</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4313,6 +5251,14 @@
       <c r="G118" t="n">
         <v>2249.25</v>
       </c>
+      <c r="H118" t="n">
+        <v>13792901235</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>南京市建邺区河西新城江东中路229号新地中心二期12A</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4346,6 +5292,14 @@
       <c r="G119" t="n">
         <v>999</v>
       </c>
+      <c r="H119" t="n">
+        <v>13803012346</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>南京市玄武区中山路228号地铁大厦1503</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4379,6 +5333,14 @@
       <c r="G120" t="n">
         <v>1274.15</v>
       </c>
+      <c r="H120" t="n">
+        <v>13803012346</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>南京市玄武区中山路228号地铁大厦1503</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4412,6 +5374,14 @@
       <c r="G121" t="n">
         <v>699</v>
       </c>
+      <c r="H121" t="n">
+        <v>13803012346</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>南京市玄武区中山路228号地铁大厦1503</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4445,6 +5415,14 @@
       <c r="G122" t="n">
         <v>2379.15</v>
       </c>
+      <c r="H122" t="n">
+        <v>13913123457</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>重庆市渝北区金开大道68号协信中心C座2001</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4478,6 +5456,14 @@
       <c r="G123" t="n">
         <v>4799.2</v>
       </c>
+      <c r="H123" t="n">
+        <v>15023234568</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>重庆市江北区观音桥步行街9号嘉年华大厦701</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4511,6 +5497,14 @@
       <c r="G124" t="n">
         <v>4399</v>
       </c>
+      <c r="H124" t="n">
+        <v>15023234568</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>重庆市江北区观音桥步行街9号嘉年华大厦701</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4544,6 +5538,14 @@
       <c r="G125" t="n">
         <v>6999</v>
       </c>
+      <c r="H125" t="n">
+        <v>15133345679</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>天津市和平区南京路189号津汇广场写字楼1座2204</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4577,6 +5579,14 @@
       <c r="G126" t="n">
         <v>3448.5</v>
       </c>
+      <c r="H126" t="n">
+        <v>15133345679</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>天津市和平区南京路189号津汇广场写字楼1座2204</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4610,6 +5620,14 @@
       <c r="G127" t="n">
         <v>11999</v>
       </c>
+      <c r="H127" t="n">
+        <v>15243456780</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>天津市南开区卫津南路109号京燕大厦B座1008</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4643,6 +5661,14 @@
       <c r="G128" t="n">
         <v>3059.15</v>
       </c>
+      <c r="H128" t="n">
+        <v>15243456780</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>天津市南开区卫津南路109号京燕大厦B座1008</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4676,6 +5702,14 @@
       <c r="G129" t="n">
         <v>524.25</v>
       </c>
+      <c r="H129" t="n">
+        <v>15243456780</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>天津市南开区卫津南路109号京燕大厦B座1008</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4709,6 +5743,14 @@
       <c r="G130" t="n">
         <v>5999</v>
       </c>
+      <c r="H130" t="n">
+        <v>15753567891</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>苏州市工业园区苏州大道西9号中海财富中心西塔1803</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4742,6 +5784,14 @@
       <c r="G131" t="n">
         <v>3199.2</v>
       </c>
+      <c r="H131" t="n">
+        <v>15753567891</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>苏州市工业园区苏州大道西9号中海财富中心西塔1803</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4775,6 +5825,14 @@
       <c r="G132" t="n">
         <v>999</v>
       </c>
+      <c r="H132" t="n">
+        <v>15753567891</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>苏州市工业园区苏州大道西9号中海财富中心西塔1803</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4808,6 +5866,14 @@
       <c r="G133" t="n">
         <v>2124.15</v>
       </c>
+      <c r="H133" t="n">
+        <v>15863678902</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>西安市雁塔区唐延路11号禾盛京广中心E座1502</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4841,6 +5907,14 @@
       <c r="G134" t="n">
         <v>2599</v>
       </c>
+      <c r="H134" t="n">
+        <v>15863678902</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>西安市雁塔区唐延路11号禾盛京广中心E座1502</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4874,6 +5948,14 @@
       <c r="G135" t="n">
         <v>319.2</v>
       </c>
+      <c r="H135" t="n">
+        <v>15863678902</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>西安市雁塔区唐延路11号禾盛京广中心E座1502</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4907,6 +5989,14 @@
       <c r="G136" t="n">
         <v>1299</v>
       </c>
+      <c r="H136" t="n">
+        <v>15863678902</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>西安市雁塔区唐延路11号禾盛京广中心E座1502</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4940,6 +6030,14 @@
       <c r="G137" t="n">
         <v>1599.2</v>
       </c>
+      <c r="H137" t="n">
+        <v>15973789013</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>长沙市芙蓉区五一大道800号中隆国际大厦1206</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4973,6 +6071,14 @@
       <c r="G138" t="n">
         <v>1999</v>
       </c>
+      <c r="H138" t="n">
+        <v>15973789013</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>长沙市芙蓉区五一大道800号中隆国际大厦1206</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5006,6 +6112,14 @@
       <c r="G139" t="n">
         <v>679.15</v>
       </c>
+      <c r="H139" t="n">
+        <v>15973789013</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>长沙市芙蓉区五一大道800号中隆国际大厦1206</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5039,6 +6153,14 @@
       <c r="G140" t="n">
         <v>6749.25</v>
       </c>
+      <c r="H140" t="n">
+        <v>18083890124</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>郑州市金水区花园路39号招银大厦2101</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5072,6 +6194,14 @@
       <c r="G141" t="n">
         <v>4999</v>
       </c>
+      <c r="H141" t="n">
+        <v>18083890124</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>郑州市金水区花园路39号招银大厦2101</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5105,6 +6235,14 @@
       <c r="G142" t="n">
         <v>7439.2</v>
       </c>
+      <c r="H142" t="n">
+        <v>18083890124</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>郑州市金水区花园路39号招银大厦2101</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5138,6 +6276,14 @@
       <c r="G143" t="n">
         <v>3059.15</v>
       </c>
+      <c r="H143" t="n">
+        <v>18083890124</v>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>郑州市金水区花园路39号招银大厦2101</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5171,6 +6317,14 @@
       <c r="G144" t="n">
         <v>1519.2</v>
       </c>
+      <c r="H144" t="n">
+        <v>18083890124</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>郑州市金水区花园路39号招银大厦2101</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5204,6 +6358,14 @@
       <c r="G145" t="n">
         <v>2099.3</v>
       </c>
+      <c r="H145" t="n">
+        <v>18083890124</v>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>郑州市金水区花园路39号招银大厦2101</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5237,6 +6399,14 @@
       <c r="G146" t="n">
         <v>6299</v>
       </c>
+      <c r="H146" t="n">
+        <v>18083890124</v>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>郑州市金水区花园路39号招银大厦2101</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5270,6 +6440,14 @@
       <c r="G147" t="n">
         <v>3299</v>
       </c>
+      <c r="H147" t="n">
+        <v>18083890124</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>郑州市金水区花园路39号招银大厦2101</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5303,6 +6481,14 @@
       <c r="G148" t="n">
         <v>1359.2</v>
       </c>
+      <c r="H148" t="n">
+        <v>18193901235</v>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>东莞市南城区鸿福路200号第一国际商务中心A座907</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5336,6 +6522,14 @@
       <c r="G149" t="n">
         <v>2174.25</v>
       </c>
+      <c r="H149" t="n">
+        <v>18193901235</v>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>东莞市南城区鸿福路200号第一国际商务中心A座907</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5369,6 +6563,14 @@
       <c r="G150" t="n">
         <v>879.2</v>
       </c>
+      <c r="H150" t="n">
+        <v>18193901235</v>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>东莞市南城区鸿福路200号第一国际商务中心A座907</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5402,6 +6604,14 @@
       <c r="G151" t="n">
         <v>279.2</v>
       </c>
+      <c r="H151" t="n">
+        <v>18193901235</v>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>东莞市南城区鸿福路200号第一国际商务中心A座907</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5435,6 +6645,14 @@
       <c r="G152" t="n">
         <v>2249.25</v>
       </c>
+      <c r="H152" t="n">
+        <v>18193901235</v>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>东莞市南城区鸿福路200号第一国际商务中心A座907</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5468,6 +6686,14 @@
       <c r="G153" t="n">
         <v>3199.2</v>
       </c>
+      <c r="H153" t="n">
+        <v>18204012346</v>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>青岛市市南区香港中路78号海航万邦中心写字楼2005</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5501,6 +6727,14 @@
       <c r="G154" t="n">
         <v>1599.2</v>
       </c>
+      <c r="H154" t="n">
+        <v>18204012346</v>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>青岛市市南区香港中路78号海航万邦中心写字楼2005</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5534,6 +6768,14 @@
       <c r="G155" t="n">
         <v>2799.3</v>
       </c>
+      <c r="H155" t="n">
+        <v>18204012346</v>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>青岛市市南区香港中路78号海航万邦中心写字楼2005</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5567,6 +6809,14 @@
       <c r="G156" t="n">
         <v>1759.2</v>
       </c>
+      <c r="H156" t="n">
+        <v>18204012346</v>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>青岛市市南区香港中路78号海航万邦中心写字楼2005</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5600,6 +6850,14 @@
       <c r="G157" t="n">
         <v>674.25</v>
       </c>
+      <c r="H157" t="n">
+        <v>18204012346</v>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>青岛市市南区香港中路78号海航万邦中心写字楼2005</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5633,6 +6891,14 @@
       <c r="G158" t="n">
         <v>1444.15</v>
       </c>
+      <c r="H158" t="n">
+        <v>18204012346</v>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>青岛市市南区香港中路78号海航万邦中心写字楼2005</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5666,6 +6932,14 @@
       <c r="G159" t="n">
         <v>1264.8</v>
       </c>
+      <c r="H159" t="n">
+        <v>18204012346</v>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>青岛市市南区香港中路78号海航万邦中心写字楼2005</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5699,6 +6973,14 @@
       <c r="G160" t="n">
         <v>9999</v>
       </c>
+      <c r="H160" t="n">
+        <v>18204012346</v>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>青岛市市南区香港中路78号海航万邦中心写字楼2005</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5732,6 +7014,14 @@
       <c r="G161" t="n">
         <v>4999</v>
       </c>
+      <c r="H161" t="n">
+        <v>18204012346</v>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>青岛市市南区香港中路78号海航万邦中心写字楼2005</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5765,6 +7055,14 @@
       <c r="G162" t="n">
         <v>4999</v>
       </c>
+      <c r="H162" t="n">
+        <v>18314123457</v>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>沈阳市沈河区青年大街219号华新国际大厦1806</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5798,6 +7096,14 @@
       <c r="G163" t="n">
         <v>2799.2</v>
       </c>
+      <c r="H163" t="n">
+        <v>18424234568</v>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>合肥市政务区潜山路888号百利商务中心北塔2202</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5831,6 +7137,14 @@
       <c r="G164" t="n">
         <v>699</v>
       </c>
+      <c r="H164" t="n">
+        <v>18424234568</v>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>合肥市政务区潜山路888号百利商务中心北塔2202</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5864,6 +7178,14 @@
       <c r="G165" t="n">
         <v>3999</v>
       </c>
+      <c r="H165" t="n">
+        <v>18534345679</v>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>福州市台江区江滨中大道378号海润滨江花园写字楼A座1205</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5897,6 +7219,14 @@
       <c r="G166" t="n">
         <v>2124.15</v>
       </c>
+      <c r="H166" t="n">
+        <v>18534345679</v>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>福州市台江区江滨中大道378号海润滨江花园写字楼A座1205</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5930,6 +7260,14 @@
       <c r="G167" t="n">
         <v>999</v>
       </c>
+      <c r="H167" t="n">
+        <v>18534345679</v>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>福州市台江区江滨中大道378号海润滨江花园写字楼A座1205</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5963,6 +7301,14 @@
       <c r="G168" t="n">
         <v>2249.25</v>
       </c>
+      <c r="H168" t="n">
+        <v>18644456780</v>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>昆明市盘龙区北京路612号银海国际公寓B座1501</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5996,6 +7342,14 @@
       <c r="G169" t="n">
         <v>2999</v>
       </c>
+      <c r="H169" t="n">
+        <v>18644456780</v>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>昆明市盘龙区北京路612号银海国际公寓B座1501</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6029,6 +7383,14 @@
       <c r="G170" t="n">
         <v>1199.2</v>
       </c>
+      <c r="H170" t="n">
+        <v>18644456780</v>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>昆明市盘龙区北京路612号银海国际公寓B座1501</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6062,6 +7424,14 @@
       <c r="G171" t="n">
         <v>2099.25</v>
       </c>
+      <c r="H171" t="n">
+        <v>18644456780</v>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>昆明市盘龙区北京路612号银海国际公寓B座1501</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -6095,6 +7465,14 @@
       <c r="G172" t="n">
         <v>3299</v>
       </c>
+      <c r="H172" t="n">
+        <v>18754567891</v>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>贵阳市观山湖区金阳南路6号世纪金源购物中心商务楼C座1802</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -6128,6 +7506,14 @@
       <c r="G173" t="n">
         <v>2639.2</v>
       </c>
+      <c r="H173" t="n">
+        <v>18754567891</v>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>贵阳市观山湖区金阳南路6号世纪金源购物中心商务楼C座1802</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6161,6 +7547,14 @@
       <c r="G174" t="n">
         <v>1299</v>
       </c>
+      <c r="H174" t="n">
+        <v>18754567891</v>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>贵阳市观山湖区金阳南路6号世纪金源购物中心商务楼C座1802</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6194,6 +7588,14 @@
       <c r="G175" t="n">
         <v>2079.2</v>
       </c>
+      <c r="H175" t="n">
+        <v>18754567891</v>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>贵阳市观山湖区金阳南路6号世纪金源购物中心商务楼C座1802</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6227,6 +7629,14 @@
       <c r="G176" t="n">
         <v>4799.2</v>
       </c>
+      <c r="H176" t="n">
+        <v>18754567891</v>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>贵阳市观山湖区金阳南路6号世纪金源购物中心商务楼C座1802</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6260,6 +7670,14 @@
       <c r="G177" t="n">
         <v>2599</v>
       </c>
+      <c r="H177" t="n">
+        <v>18864678902</v>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>南宁市青秀区民族大道146号三祺广场写字楼2206</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6293,6 +7711,14 @@
       <c r="G178" t="n">
         <v>1999</v>
       </c>
+      <c r="H178" t="n">
+        <v>18864678902</v>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>南宁市青秀区民族大道146号三祺广场写字楼2206</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6326,6 +7752,14 @@
       <c r="G179" t="n">
         <v>879.2</v>
       </c>
+      <c r="H179" t="n">
+        <v>18864678902</v>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>南宁市青秀区民族大道146号三祺广场写字楼2206</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6359,6 +7793,14 @@
       <c r="G180" t="n">
         <v>1264.8</v>
       </c>
+      <c r="H180" t="n">
+        <v>18864678902</v>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>南宁市青秀区民族大道146号三祺广场写字楼2206</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6392,6 +7834,14 @@
       <c r="G181" t="n">
         <v>7499</v>
       </c>
+      <c r="H181" t="n">
+        <v>18864678902</v>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>南宁市青秀区民族大道146号三祺广场写字楼2206</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6425,6 +7875,14 @@
       <c r="G182" t="n">
         <v>1799.1</v>
       </c>
+      <c r="H182" t="n">
+        <v>18864678902</v>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>南宁市青秀区民族大道146号三祺广场写字楼2206</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6458,6 +7916,14 @@
       <c r="G183" t="n">
         <v>1359.15</v>
       </c>
+      <c r="H183" t="n">
+        <v>18974789013</v>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>兰州市城关区张掖路87号中环广场写字楼A座1103</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6491,6 +7957,14 @@
       <c r="G184" t="n">
         <v>2174.25</v>
       </c>
+      <c r="H184" t="n">
+        <v>18974789013</v>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>兰州市城关区张掖路87号中环广场写字楼A座1103</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6524,6 +7998,14 @@
       <c r="G185" t="n">
         <v>399.2</v>
       </c>
+      <c r="H185" t="n">
+        <v>18974789013</v>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>兰州市城关区张掖路87号中环广场写字楼A座1103</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6557,6 +8039,14 @@
       <c r="G186" t="n">
         <v>899.1</v>
       </c>
+      <c r="H186" t="n">
+        <v>18974789013</v>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>兰州市城关区张掖路87号中环广场写字楼A座1103</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6590,6 +8080,14 @@
       <c r="G187" t="n">
         <v>5949.15</v>
       </c>
+      <c r="H187" t="n">
+        <v>18974789013</v>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>兰州市城关区张掖路87号中环广场写字楼A座1103</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6623,6 +8121,14 @@
       <c r="G188" t="n">
         <v>3059.15</v>
       </c>
+      <c r="H188" t="n">
+        <v>18974789013</v>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>兰州市城关区张掖路87号中环广场写字楼A座1103</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6656,6 +8162,14 @@
       <c r="G189" t="n">
         <v>719.2</v>
       </c>
+      <c r="H189" t="n">
+        <v>18974789013</v>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>兰州市城关区张掖路87号中环广场写字楼A座1103</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6689,6 +8203,14 @@
       <c r="G190" t="n">
         <v>2159.2</v>
       </c>
+      <c r="H190" t="n">
+        <v>13084890124</v>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>乌鲁木齐市天山区新华北路165号中信银行大厦20F</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6722,6 +8244,14 @@
       <c r="G191" t="n">
         <v>2899</v>
       </c>
+      <c r="H191" t="n">
+        <v>13084890124</v>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>乌鲁木齐市天山区新华北路165号中信银行大厦20F</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6755,6 +8285,14 @@
       <c r="G192" t="n">
         <v>2799.3</v>
       </c>
+      <c r="H192" t="n">
+        <v>13084890124</v>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>乌鲁木齐市天山区新华北路165号中信银行大厦20F</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6788,6 +8326,14 @@
       <c r="G193" t="n">
         <v>679.15</v>
       </c>
+      <c r="H193" t="n">
+        <v>13084890124</v>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>乌鲁木齐市天山区新华北路165号中信银行大厦20F</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6821,6 +8367,14 @@
       <c r="G194" t="n">
         <v>319.2</v>
       </c>
+      <c r="H194" t="n">
+        <v>13084890124</v>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>乌鲁木齐市天山区新华北路165号中信银行大厦20F</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6854,6 +8408,14 @@
       <c r="G195" t="n">
         <v>1299</v>
       </c>
+      <c r="H195" t="n">
+        <v>13084890124</v>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>乌鲁木齐市天山区新华北路165号中信银行大厦20F</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6887,6 +8449,14 @@
       <c r="G196" t="n">
         <v>6449.25</v>
       </c>
+      <c r="H196" t="n">
+        <v>13084890124</v>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>乌鲁木齐市天山区新华北路165号中信银行大厦20F</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6920,6 +8490,14 @@
       <c r="G197" t="n">
         <v>999</v>
       </c>
+      <c r="H197" t="n">
+        <v>13084890124</v>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>乌鲁木齐市天山区新华北路165号中信银行大厦20F</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6953,6 +8531,14 @@
       <c r="G198" t="n">
         <v>1599.2</v>
       </c>
+      <c r="H198" t="n">
+        <v>13194901235</v>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>哈尔滨市南岗区红军街15号奥威斯大厦1503</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6986,6 +8572,14 @@
       <c r="G199" t="n">
         <v>3199.2</v>
       </c>
+      <c r="H199" t="n">
+        <v>13194901235</v>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>哈尔滨市南岗区红军街15号奥威斯大厦1503</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -7019,6 +8613,14 @@
       <c r="G200" t="n">
         <v>2099.3</v>
       </c>
+      <c r="H200" t="n">
+        <v>13194901235</v>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>哈尔滨市南岗区红军街15号奥威斯大厦1503</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -7051,6 +8653,14 @@
       </c>
       <c r="G201" t="n">
         <v>4799.2</v>
+      </c>
+      <c r="H201" t="n">
+        <v>13205012346</v>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>长春市朝阳区同志街2222号通源国际大厦B座1208</t>
+        </is>
       </c>
     </row>
   </sheetData>
